--- a/Data/EXCEL/Transfer/salemon/202206/4174-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/4174-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BCC45370-46D6-4D1A-BA04-B57A05762CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{511BBE27-5984-48DA-A79F-B47C4B062FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="4174-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -1218,20 +1218,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q125"/>
+  <dimension ref="A1:Q126"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.75" customWidth="1"/>
-    <col min="2" max="6" width="9.875" customWidth="1"/>
-    <col min="7" max="7" width="10.75" customWidth="1"/>
-    <col min="8" max="8" width="11.25" customWidth="1"/>
-    <col min="9" max="9" width="12.75" customWidth="1"/>
-    <col min="10" max="11" width="11.25" customWidth="1"/>
-    <col min="12" max="12" width="12.75" customWidth="1"/>
-    <col min="13" max="13" width="11.25" customWidth="1"/>
-    <col min="14" max="14" width="12.75" customWidth="1"/>
-    <col min="15" max="16" width="11.25" customWidth="1"/>
-    <col min="17" max="17" width="13.625" customWidth="1"/>
+    <col min="1" max="1" width="12.875" customWidth="1"/>
+    <col min="2" max="6" width="10.75" customWidth="1"/>
+    <col min="7" max="7" width="11.875" customWidth="1"/>
+    <col min="8" max="8" width="12.375" customWidth="1"/>
+    <col min="9" max="9" width="13.875" customWidth="1"/>
+    <col min="10" max="11" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="13.875" customWidth="1"/>
+    <col min="13" max="13" width="12.375" customWidth="1"/>
+    <col min="14" max="14" width="13.875" customWidth="1"/>
+    <col min="15" max="16" width="12.375" customWidth="1"/>
+    <col min="17" max="17" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1384,900 +1384,900 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>110.5</v>
+        <v>111</v>
       </c>
       <c r="C5" s="7">
-        <v>110.5</v>
+        <v>97.5</v>
       </c>
       <c r="D5" s="7">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E5" s="7">
-        <v>107.5</v>
+        <v>96.5</v>
       </c>
       <c r="F5" s="8">
-        <v>-1</v>
+        <v>-13</v>
       </c>
       <c r="G5" s="8">
-        <v>-0.9</v>
+        <v>-11.76</v>
       </c>
       <c r="H5" s="9">
-        <v>1.2800000000000001E-2</v>
-      </c>
-      <c r="I5" s="10">
-        <v>1423.8</v>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I5" s="8">
+        <v>-60.6</v>
       </c>
       <c r="J5" s="8">
-        <v>-83.3</v>
+        <v>-38.1</v>
       </c>
       <c r="K5" s="9">
-        <v>2.6200000000000001E-2</v>
+        <v>3.1300000000000001E-2</v>
       </c>
       <c r="L5" s="8">
-        <v>-79.3</v>
+        <v>-76.8</v>
       </c>
       <c r="M5" s="9">
-        <v>1.2800000000000001E-2</v>
-      </c>
-      <c r="N5" s="10">
-        <v>1423.8</v>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="N5" s="8">
+        <v>-60.6</v>
       </c>
       <c r="O5" s="8">
-        <v>-83.3</v>
+        <v>-38.1</v>
       </c>
       <c r="P5" s="9">
-        <v>2.6200000000000001E-2</v>
+        <v>3.1300000000000001E-2</v>
       </c>
       <c r="Q5" s="8">
-        <v>-79.3</v>
+        <v>-76.8</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
-        <v>111</v>
+        <v>110.5</v>
       </c>
       <c r="C6" s="7">
-        <v>111.5</v>
+        <v>110.5</v>
       </c>
       <c r="D6" s="7">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E6" s="7">
-        <v>104.5</v>
-      </c>
-      <c r="F6" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="G6" s="10">
-        <v>0.45</v>
+        <v>107.5</v>
+      </c>
+      <c r="F6" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G6" s="8">
+        <v>-0.9</v>
       </c>
       <c r="H6" s="9">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="I6" s="8">
-        <v>-84.9</v>
+        <v>1.2800000000000001E-2</v>
+      </c>
+      <c r="I6" s="10">
+        <v>1423.8</v>
       </c>
       <c r="J6" s="8">
-        <v>-84.2</v>
+        <v>-83.3</v>
       </c>
       <c r="K6" s="9">
-        <v>1.34E-2</v>
+        <v>2.6200000000000001E-2</v>
       </c>
       <c r="L6" s="8">
-        <v>-73</v>
+        <v>-79.3</v>
       </c>
       <c r="M6" s="9">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="N6" s="8">
-        <v>-84.9</v>
+        <v>1.2800000000000001E-2</v>
+      </c>
+      <c r="N6" s="10">
+        <v>1423.8</v>
       </c>
       <c r="O6" s="8">
-        <v>-84.2</v>
+        <v>-83.3</v>
       </c>
       <c r="P6" s="9">
-        <v>1.34E-2</v>
+        <v>2.6200000000000001E-2</v>
       </c>
       <c r="Q6" s="8">
-        <v>-73</v>
+        <v>-79.3</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
+        <v>111</v>
+      </c>
+      <c r="C7" s="7">
+        <v>111.5</v>
+      </c>
+      <c r="D7" s="7">
         <v>115</v>
       </c>
-      <c r="C7" s="7">
-        <v>111</v>
-      </c>
-      <c r="D7" s="7">
-        <v>116.5</v>
-      </c>
       <c r="E7" s="7">
-        <v>106</v>
-      </c>
-      <c r="F7" s="8">
-        <v>-6</v>
-      </c>
-      <c r="G7" s="8">
-        <v>-5.13</v>
+        <v>104.5</v>
+      </c>
+      <c r="F7" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="10">
+        <v>0.45</v>
       </c>
       <c r="H7" s="9">
-        <v>5.5999999999999999E-3</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="I7" s="8">
-        <v>-21.4</v>
-      </c>
-      <c r="J7" s="10">
-        <v>74.5</v>
+        <v>-84.9</v>
+      </c>
+      <c r="J7" s="8">
+        <v>-84.2</v>
       </c>
       <c r="K7" s="9">
-        <v>1.26E-2</v>
+        <v>1.34E-2</v>
       </c>
       <c r="L7" s="8">
-        <v>-71.7</v>
+        <v>-73</v>
       </c>
       <c r="M7" s="9">
-        <v>5.5999999999999999E-3</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="N7" s="8">
-        <v>-21.4</v>
-      </c>
-      <c r="O7" s="10">
-        <v>74.5</v>
+        <v>-84.9</v>
+      </c>
+      <c r="O7" s="8">
+        <v>-84.2</v>
       </c>
       <c r="P7" s="9">
-        <v>1.26E-2</v>
+        <v>1.34E-2</v>
       </c>
       <c r="Q7" s="8">
-        <v>-71.7</v>
+        <v>-73</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="C8" s="7">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D8" s="7">
-        <v>137.5</v>
+        <v>116.5</v>
       </c>
       <c r="E8" s="7">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F8" s="8">
-        <v>-1.5</v>
+        <v>-6</v>
       </c>
       <c r="G8" s="8">
-        <v>-1.27</v>
+        <v>-5.13</v>
       </c>
       <c r="H8" s="9">
-        <v>7.1000000000000004E-3</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>17</v>
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="I8" s="8">
+        <v>-21.4</v>
       </c>
       <c r="J8" s="10">
-        <v>5330.8</v>
+        <v>74.5</v>
       </c>
       <c r="K8" s="9">
-        <v>7.1000000000000004E-3</v>
+        <v>1.26E-2</v>
       </c>
       <c r="L8" s="8">
-        <v>-83</v>
+        <v>-71.7</v>
       </c>
       <c r="M8" s="9">
-        <v>7.1000000000000004E-3</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>17</v>
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="N8" s="8">
+        <v>-21.4</v>
       </c>
       <c r="O8" s="10">
-        <v>5330.8</v>
+        <v>74.5</v>
       </c>
       <c r="P8" s="9">
-        <v>7.1000000000000004E-3</v>
+        <v>1.26E-2</v>
       </c>
       <c r="Q8" s="8">
-        <v>-83</v>
+        <v>-71.7</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B9" s="7">
-        <v>114.5</v>
+        <v>128</v>
       </c>
       <c r="C9" s="7">
-        <v>118.5</v>
+        <v>117</v>
       </c>
       <c r="D9" s="7">
-        <v>118.5</v>
+        <v>137.5</v>
       </c>
       <c r="E9" s="7">
-        <v>105.5</v>
-      </c>
-      <c r="F9" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="G9" s="10">
-        <v>3.95</v>
+        <v>113</v>
+      </c>
+      <c r="F9" s="8">
+        <v>-1.5</v>
+      </c>
+      <c r="G9" s="8">
+        <v>-1.27</v>
       </c>
       <c r="H9" s="9">
-        <v>0</v>
-      </c>
-      <c r="I9" s="8">
-        <v>-100</v>
-      </c>
-      <c r="J9" s="8">
-        <v>-100</v>
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="10">
+        <v>5330.8</v>
       </c>
       <c r="K9" s="9">
-        <v>0</v>
+        <v>7.1000000000000004E-3</v>
       </c>
       <c r="L9" s="8">
-        <v>-100</v>
+        <v>-83</v>
       </c>
       <c r="M9" s="9">
-        <v>0</v>
-      </c>
-      <c r="N9" s="8">
-        <v>-100</v>
-      </c>
-      <c r="O9" s="8">
-        <v>-100</v>
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O9" s="10">
+        <v>5330.8</v>
       </c>
       <c r="P9" s="9">
-        <v>0</v>
+        <v>7.1000000000000004E-3</v>
       </c>
       <c r="Q9" s="8">
-        <v>-100</v>
+        <v>-83</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B10" s="7">
-        <v>105</v>
+        <v>114.5</v>
       </c>
       <c r="C10" s="7">
-        <v>114</v>
+        <v>118.5</v>
       </c>
       <c r="D10" s="7">
-        <v>128</v>
+        <v>118.5</v>
       </c>
       <c r="E10" s="7">
-        <v>101.5</v>
+        <v>105.5</v>
       </c>
       <c r="F10" s="10">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="G10" s="10">
-        <v>6.54</v>
+        <v>3.95</v>
       </c>
       <c r="H10" s="9">
-        <v>7.1000000000000004E-3</v>
-      </c>
-      <c r="I10" s="10">
-        <v>545.4</v>
-      </c>
-      <c r="J10" s="10">
-        <v>82.5</v>
+        <v>0</v>
+      </c>
+      <c r="I10" s="8">
+        <v>-100</v>
+      </c>
+      <c r="J10" s="8">
+        <v>-100</v>
       </c>
       <c r="K10" s="9">
-        <v>0.188</v>
+        <v>0</v>
       </c>
       <c r="L10" s="8">
-        <v>-86.5</v>
+        <v>-100</v>
       </c>
       <c r="M10" s="9">
-        <v>7.1000000000000004E-3</v>
-      </c>
-      <c r="N10" s="10">
-        <v>545.4</v>
-      </c>
-      <c r="O10" s="10">
-        <v>82.5</v>
+        <v>0</v>
+      </c>
+      <c r="N10" s="8">
+        <v>-100</v>
+      </c>
+      <c r="O10" s="8">
+        <v>-100</v>
       </c>
       <c r="P10" s="9">
-        <v>0.188</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="8">
-        <v>-86.5</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B11" s="7">
-        <v>106.5</v>
+        <v>105</v>
       </c>
       <c r="C11" s="7">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D11" s="7">
-        <v>116.5</v>
+        <v>128</v>
       </c>
       <c r="E11" s="7">
-        <v>99.6</v>
+        <v>101.5</v>
       </c>
       <c r="F11" s="10">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="G11" s="10">
-        <v>0.47</v>
+        <v>6.54</v>
       </c>
       <c r="H11" s="9">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="I11" s="8">
-        <v>-93.5</v>
-      </c>
-      <c r="J11" s="8">
-        <v>-99.8</v>
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="I11" s="10">
+        <v>545.4</v>
+      </c>
+      <c r="J11" s="10">
+        <v>82.5</v>
       </c>
       <c r="K11" s="9">
-        <v>0.18099999999999999</v>
+        <v>0.188</v>
       </c>
       <c r="L11" s="8">
-        <v>-87</v>
+        <v>-86.5</v>
       </c>
       <c r="M11" s="9">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="N11" s="8">
-        <v>-93.5</v>
-      </c>
-      <c r="O11" s="8">
-        <v>-99.8</v>
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="N11" s="10">
+        <v>545.4</v>
+      </c>
+      <c r="O11" s="10">
+        <v>82.5</v>
       </c>
       <c r="P11" s="9">
-        <v>0.18099999999999999</v>
+        <v>0.188</v>
       </c>
       <c r="Q11" s="8">
-        <v>-87</v>
+        <v>-86.5</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B12" s="7">
-        <v>104</v>
+        <v>106.5</v>
       </c>
       <c r="C12" s="7">
-        <v>106.5</v>
+        <v>107</v>
       </c>
       <c r="D12" s="7">
-        <v>112</v>
+        <v>116.5</v>
       </c>
       <c r="E12" s="7">
-        <v>96.3</v>
+        <v>99.6</v>
       </c>
       <c r="F12" s="10">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="G12" s="10">
-        <v>2.4</v>
+        <v>0.47</v>
       </c>
       <c r="H12" s="9">
-        <v>1.6899999999999998E-2</v>
-      </c>
-      <c r="I12" s="10">
-        <v>285</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>17</v>
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="I12" s="8">
+        <v>-93.5</v>
+      </c>
+      <c r="J12" s="8">
+        <v>-99.8</v>
       </c>
       <c r="K12" s="9">
-        <v>0.18</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="L12" s="8">
-        <v>-70.599999999999994</v>
+        <v>-87</v>
       </c>
       <c r="M12" s="9">
-        <v>1.6899999999999998E-2</v>
-      </c>
-      <c r="N12" s="10">
-        <v>285</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>17</v>
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="N12" s="8">
+        <v>-93.5</v>
+      </c>
+      <c r="O12" s="8">
+        <v>-99.8</v>
       </c>
       <c r="P12" s="9">
-        <v>0.18</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="Q12" s="8">
-        <v>-70.599999999999994</v>
+        <v>-87</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B13" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C13" s="7">
-        <v>104</v>
+        <v>106.5</v>
       </c>
       <c r="D13" s="7">
-        <v>116.5</v>
+        <v>112</v>
       </c>
       <c r="E13" s="7">
-        <v>101</v>
+        <v>96.3</v>
       </c>
       <c r="F13" s="10">
         <v>2.5</v>
       </c>
       <c r="G13" s="10">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="H13" s="9">
-        <v>4.4000000000000003E-3</v>
-      </c>
-      <c r="I13" s="8">
-        <v>-36</v>
-      </c>
-      <c r="J13" s="8">
-        <v>-20.8</v>
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="I13" s="10">
+        <v>285</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K13" s="9">
-        <v>0.16300000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="L13" s="8">
-        <v>-73.3</v>
+        <v>-70.599999999999994</v>
       </c>
       <c r="M13" s="9">
-        <v>4.4000000000000003E-3</v>
-      </c>
-      <c r="N13" s="8">
-        <v>-36</v>
-      </c>
-      <c r="O13" s="8">
-        <v>-20.8</v>
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="N13" s="10">
+        <v>285</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P13" s="9">
-        <v>0.16300000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="Q13" s="8">
-        <v>-73.3</v>
+        <v>-70.599999999999994</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B14" s="7">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C14" s="7">
-        <v>101.5</v>
+        <v>104</v>
       </c>
       <c r="D14" s="7">
-        <v>109</v>
+        <v>116.5</v>
       </c>
       <c r="E14" s="7">
-        <v>93.4</v>
-      </c>
-      <c r="F14" s="8">
-        <v>-7</v>
-      </c>
-      <c r="G14" s="8">
-        <v>-6.45</v>
+        <v>101</v>
+      </c>
+      <c r="F14" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="G14" s="10">
+        <v>2.46</v>
       </c>
       <c r="H14" s="9">
-        <v>6.8999999999999999E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="I14" s="8">
-        <v>-58.7</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>17</v>
+        <v>-36</v>
+      </c>
+      <c r="J14" s="8">
+        <v>-20.8</v>
       </c>
       <c r="K14" s="9">
-        <v>0.158</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="L14" s="8">
-        <v>-73.8</v>
+        <v>-73.3</v>
       </c>
       <c r="M14" s="9">
-        <v>6.8999999999999999E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="N14" s="8">
-        <v>-58.7</v>
-      </c>
-      <c r="O14" s="9" t="s">
-        <v>17</v>
+        <v>-36</v>
+      </c>
+      <c r="O14" s="8">
+        <v>-20.8</v>
       </c>
       <c r="P14" s="9">
-        <v>0.158</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="Q14" s="8">
-        <v>-73.8</v>
+        <v>-73.3</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B15" s="7">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C15" s="7">
-        <v>108.5</v>
+        <v>101.5</v>
       </c>
       <c r="D15" s="7">
-        <v>116.5</v>
+        <v>109</v>
       </c>
       <c r="E15" s="7">
-        <v>101.5</v>
+        <v>93.4</v>
       </c>
       <c r="F15" s="8">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="G15" s="8">
-        <v>-4.41</v>
+        <v>-6.45</v>
       </c>
       <c r="H15" s="9">
-        <v>1.66E-2</v>
-      </c>
-      <c r="I15" s="10">
-        <v>104</v>
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="I15" s="8">
+        <v>-58.7</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K15" s="9">
-        <v>0.151</v>
+        <v>0.158</v>
       </c>
       <c r="L15" s="8">
-        <v>-75</v>
+        <v>-73.8</v>
       </c>
       <c r="M15" s="9">
-        <v>1.66E-2</v>
-      </c>
-      <c r="N15" s="10">
-        <v>104</v>
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="N15" s="8">
+        <v>-58.7</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P15" s="9">
-        <v>0.151</v>
+        <v>0.158</v>
       </c>
       <c r="Q15" s="8">
-        <v>-75</v>
+        <v>-73.8</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B16" s="7">
         <v>115</v>
       </c>
       <c r="C16" s="7">
-        <v>113.5</v>
+        <v>108.5</v>
       </c>
       <c r="D16" s="7">
-        <v>125.5</v>
+        <v>116.5</v>
       </c>
       <c r="E16" s="7">
-        <v>113</v>
+        <v>101.5</v>
       </c>
       <c r="F16" s="8">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="G16" s="8">
-        <v>-0.87</v>
+        <v>-4.41</v>
       </c>
       <c r="H16" s="9">
-        <v>8.0999999999999996E-3</v>
-      </c>
-      <c r="I16" s="8">
-        <v>-89.4</v>
-      </c>
-      <c r="J16" s="10">
-        <v>204.9</v>
+        <v>1.66E-2</v>
+      </c>
+      <c r="I16" s="10">
+        <v>104</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K16" s="9">
-        <v>0.13500000000000001</v>
+        <v>0.151</v>
       </c>
       <c r="L16" s="8">
-        <v>-77.7</v>
+        <v>-75</v>
       </c>
       <c r="M16" s="9">
-        <v>8.0999999999999996E-3</v>
-      </c>
-      <c r="N16" s="8">
-        <v>-89.4</v>
-      </c>
-      <c r="O16" s="10">
-        <v>204.9</v>
+        <v>1.66E-2</v>
+      </c>
+      <c r="N16" s="10">
+        <v>104</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P16" s="9">
-        <v>0.13500000000000001</v>
+        <v>0.151</v>
       </c>
       <c r="Q16" s="8">
-        <v>-77.7</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B17" s="7">
-        <v>132.5</v>
+        <v>115</v>
       </c>
       <c r="C17" s="7">
-        <v>114.5</v>
+        <v>113.5</v>
       </c>
       <c r="D17" s="7">
-        <v>136</v>
+        <v>125.5</v>
       </c>
       <c r="E17" s="7">
-        <v>106.5</v>
+        <v>113</v>
       </c>
       <c r="F17" s="8">
-        <v>-17</v>
+        <v>-1</v>
       </c>
       <c r="G17" s="8">
-        <v>-12.93</v>
+        <v>-0.87</v>
       </c>
       <c r="H17" s="9">
-        <v>7.6700000000000004E-2</v>
-      </c>
-      <c r="I17" s="10">
-        <v>1347.5</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>17</v>
+        <v>8.0999999999999996E-3</v>
+      </c>
+      <c r="I17" s="8">
+        <v>-89.4</v>
+      </c>
+      <c r="J17" s="10">
+        <v>204.9</v>
       </c>
       <c r="K17" s="9">
-        <v>0.127</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="L17" s="8">
-        <v>-79</v>
+        <v>-77.7</v>
       </c>
       <c r="M17" s="9">
-        <v>7.6700000000000004E-2</v>
-      </c>
-      <c r="N17" s="10">
-        <v>1347.5</v>
-      </c>
-      <c r="O17" s="9" t="s">
-        <v>17</v>
+        <v>8.0999999999999996E-3</v>
+      </c>
+      <c r="N17" s="8">
+        <v>-89.4</v>
+      </c>
+      <c r="O17" s="10">
+        <v>204.9</v>
       </c>
       <c r="P17" s="9">
-        <v>0.127</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="Q17" s="8">
-        <v>-79</v>
+        <v>-77.7</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B18" s="7">
-        <v>150</v>
+        <v>132.5</v>
       </c>
       <c r="C18" s="7">
-        <v>131.5</v>
+        <v>114.5</v>
       </c>
       <c r="D18" s="7">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="E18" s="7">
-        <v>129</v>
+        <v>106.5</v>
       </c>
       <c r="F18" s="8">
-        <v>-18.5</v>
+        <v>-17</v>
       </c>
       <c r="G18" s="8">
-        <v>-12.33</v>
+        <v>-12.93</v>
       </c>
       <c r="H18" s="9">
-        <v>5.3E-3</v>
+        <v>7.6700000000000004E-2</v>
       </c>
       <c r="I18" s="10">
-        <v>66.7</v>
-      </c>
-      <c r="J18" s="8">
-        <v>-99.1</v>
+        <v>1347.5</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K18" s="9">
-        <v>4.99E-2</v>
+        <v>0.127</v>
       </c>
       <c r="L18" s="8">
-        <v>-91.7</v>
+        <v>-79</v>
       </c>
       <c r="M18" s="9">
-        <v>5.3E-3</v>
+        <v>7.6700000000000004E-2</v>
       </c>
       <c r="N18" s="10">
-        <v>66.7</v>
-      </c>
-      <c r="O18" s="8">
-        <v>-99.1</v>
+        <v>1347.5</v>
+      </c>
+      <c r="O18" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P18" s="9">
-        <v>4.99E-2</v>
+        <v>0.127</v>
       </c>
       <c r="Q18" s="8">
-        <v>-91.7</v>
+        <v>-79</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B19" s="7">
         <v>150</v>
       </c>
       <c r="C19" s="7">
+        <v>131.5</v>
+      </c>
+      <c r="D19" s="7">
         <v>150</v>
       </c>
-      <c r="D19" s="7">
-        <v>163</v>
-      </c>
       <c r="E19" s="7">
-        <v>141</v>
-      </c>
-      <c r="F19" s="10">
-        <v>10.5</v>
-      </c>
-      <c r="G19" s="10">
-        <v>7.53</v>
+        <v>129</v>
+      </c>
+      <c r="F19" s="8">
+        <v>-18.5</v>
+      </c>
+      <c r="G19" s="8">
+        <v>-12.33</v>
       </c>
       <c r="H19" s="9">
-        <v>3.2000000000000002E-3</v>
+        <v>5.3E-3</v>
       </c>
       <c r="I19" s="10">
-        <v>2346.1999999999998</v>
-      </c>
-      <c r="J19" s="10">
-        <v>14</v>
+        <v>66.7</v>
+      </c>
+      <c r="J19" s="8">
+        <v>-99.1</v>
       </c>
       <c r="K19" s="9">
-        <v>4.4600000000000001E-2</v>
-      </c>
-      <c r="L19" s="10">
-        <v>1498.6</v>
+        <v>4.99E-2</v>
+      </c>
+      <c r="L19" s="8">
+        <v>-91.7</v>
       </c>
       <c r="M19" s="9">
-        <v>3.2000000000000002E-3</v>
+        <v>5.3E-3</v>
       </c>
       <c r="N19" s="10">
-        <v>2346.1999999999998</v>
-      </c>
-      <c r="O19" s="10">
-        <v>14</v>
+        <v>66.7</v>
+      </c>
+      <c r="O19" s="8">
+        <v>-99.1</v>
       </c>
       <c r="P19" s="9">
-        <v>4.4600000000000001E-2</v>
-      </c>
-      <c r="Q19" s="10">
-        <v>1498.6</v>
+        <v>4.99E-2</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>-91.7</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B20" s="7">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="C20" s="7">
-        <v>139.5</v>
+        <v>150</v>
       </c>
       <c r="D20" s="7">
-        <v>139.5</v>
+        <v>163</v>
       </c>
       <c r="E20" s="7">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="F20" s="10">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="G20" s="10">
-        <v>21.83</v>
+        <v>7.53</v>
       </c>
       <c r="H20" s="9">
-        <v>1E-4</v>
-      </c>
-      <c r="I20" s="8">
-        <v>-99.7</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>17</v>
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="I20" s="10">
+        <v>2346.1999999999998</v>
+      </c>
+      <c r="J20" s="10">
+        <v>14</v>
       </c>
       <c r="K20" s="9">
-        <v>4.1399999999999999E-2</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>17</v>
+        <v>4.4600000000000001E-2</v>
+      </c>
+      <c r="L20" s="10">
+        <v>1498.6</v>
       </c>
       <c r="M20" s="9">
-        <v>1E-4</v>
-      </c>
-      <c r="N20" s="8">
-        <v>-99.7</v>
-      </c>
-      <c r="O20" s="9" t="s">
-        <v>17</v>
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="N20" s="10">
+        <v>2346.1999999999998</v>
+      </c>
+      <c r="O20" s="10">
+        <v>14</v>
       </c>
       <c r="P20" s="9">
-        <v>4.1399999999999999E-2</v>
-      </c>
-      <c r="Q20" s="9" t="s">
-        <v>17</v>
+        <v>4.4600000000000001E-2</v>
+      </c>
+      <c r="Q20" s="10">
+        <v>1498.6</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B21" s="7">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="C21" s="7">
-        <v>114.5</v>
+        <v>139.5</v>
       </c>
       <c r="D21" s="7">
-        <v>140</v>
+        <v>139.5</v>
       </c>
       <c r="E21" s="7">
         <v>113</v>
       </c>
-      <c r="F21" s="8">
-        <v>-24.5</v>
-      </c>
-      <c r="G21" s="8">
-        <v>-17.63</v>
+      <c r="F21" s="10">
+        <v>25</v>
+      </c>
+      <c r="G21" s="10">
+        <v>21.83</v>
       </c>
       <c r="H21" s="9">
-        <v>4.1300000000000003E-2</v>
-      </c>
-      <c r="I21" s="10">
-        <v>961.4</v>
+        <v>1E-4</v>
+      </c>
+      <c r="I21" s="8">
+        <v>-99.7</v>
       </c>
       <c r="J21" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K21" s="9">
-        <v>4.1300000000000003E-2</v>
+        <v>4.1399999999999999E-2</v>
       </c>
       <c r="L21" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M21" s="9">
-        <v>4.1300000000000003E-2</v>
-      </c>
-      <c r="N21" s="10">
-        <v>961.4</v>
+        <v>1E-4</v>
+      </c>
+      <c r="N21" s="8">
+        <v>-99.7</v>
       </c>
       <c r="O21" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P21" s="9">
-        <v>4.1300000000000003E-2</v>
+        <v>4.1399999999999999E-2</v>
       </c>
       <c r="Q21" s="9" t="s">
         <v>17</v>
@@ -2285,193 +2285,193 @@
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B22" s="7">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="C22" s="7">
-        <v>139</v>
+        <v>114.5</v>
       </c>
       <c r="D22" s="7">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E22" s="7">
         <v>113</v>
       </c>
-      <c r="F22" s="10">
-        <v>21</v>
-      </c>
-      <c r="G22" s="10">
-        <v>17.8</v>
+      <c r="F22" s="8">
+        <v>-24.5</v>
+      </c>
+      <c r="G22" s="8">
+        <v>-17.63</v>
       </c>
       <c r="H22" s="9">
-        <v>3.8999999999999998E-3</v>
-      </c>
-      <c r="I22" s="8">
-        <v>-99.5</v>
-      </c>
-      <c r="J22" s="10">
-        <v>27.5</v>
+        <v>4.1300000000000003E-2</v>
+      </c>
+      <c r="I22" s="10">
+        <v>961.4</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K22" s="9">
-        <v>1.39</v>
-      </c>
-      <c r="L22" s="10">
-        <v>15846</v>
+        <v>4.1300000000000003E-2</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M22" s="9">
-        <v>3.8999999999999998E-3</v>
-      </c>
-      <c r="N22" s="8">
-        <v>-99.5</v>
-      </c>
-      <c r="O22" s="10">
-        <v>27.5</v>
+        <v>4.1300000000000003E-2</v>
+      </c>
+      <c r="N22" s="10">
+        <v>961.4</v>
+      </c>
+      <c r="O22" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P22" s="9">
-        <v>1.39</v>
-      </c>
-      <c r="Q22" s="10">
-        <v>15846</v>
+        <v>4.1300000000000003E-2</v>
+      </c>
+      <c r="Q22" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B23" s="7">
-        <v>111.5</v>
+        <v>118</v>
       </c>
       <c r="C23" s="7">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="D23" s="7">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="E23" s="7">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F23" s="10">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="G23" s="10">
-        <v>6.31</v>
+        <v>17.8</v>
       </c>
       <c r="H23" s="9">
-        <v>0.77600000000000002</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>17</v>
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="I23" s="8">
+        <v>-99.5</v>
+      </c>
+      <c r="J23" s="10">
+        <v>27.5</v>
       </c>
       <c r="K23" s="9">
         <v>1.39</v>
       </c>
       <c r="L23" s="10">
-        <v>24355</v>
+        <v>15846</v>
       </c>
       <c r="M23" s="9">
-        <v>0.77600000000000002</v>
-      </c>
-      <c r="N23" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O23" s="9" t="s">
-        <v>17</v>
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="N23" s="8">
+        <v>-99.5</v>
+      </c>
+      <c r="O23" s="10">
+        <v>27.5</v>
       </c>
       <c r="P23" s="9">
         <v>1.39</v>
       </c>
       <c r="Q23" s="10">
-        <v>24355</v>
+        <v>15846</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B24" s="7">
-        <v>111</v>
+        <v>111.5</v>
       </c>
       <c r="C24" s="7">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D24" s="7">
-        <v>122.5</v>
+        <v>123</v>
       </c>
       <c r="E24" s="7">
-        <v>108</v>
-      </c>
-      <c r="F24" s="8">
-        <v>-1</v>
-      </c>
-      <c r="G24" s="8">
-        <v>-0.89</v>
+        <v>109</v>
+      </c>
+      <c r="F24" s="10">
+        <v>7</v>
+      </c>
+      <c r="G24" s="10">
+        <v>6.31</v>
       </c>
       <c r="H24" s="9">
-        <v>0</v>
-      </c>
-      <c r="I24" s="8">
-        <v>-100</v>
+        <v>0.77600000000000002</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K24" s="9">
-        <v>0.61</v>
+        <v>1.39</v>
       </c>
       <c r="L24" s="10">
-        <v>10661.9</v>
+        <v>24355</v>
       </c>
       <c r="M24" s="9">
-        <v>0</v>
-      </c>
-      <c r="N24" s="8">
-        <v>-100</v>
+        <v>0.77600000000000002</v>
+      </c>
+      <c r="N24" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O24" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P24" s="9">
-        <v>0.61</v>
+        <v>1.39</v>
       </c>
       <c r="Q24" s="10">
-        <v>10661.9</v>
+        <v>24355</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B25" s="7">
-        <v>119.5</v>
+        <v>111</v>
       </c>
       <c r="C25" s="7">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D25" s="7">
-        <v>119.5</v>
+        <v>122.5</v>
       </c>
       <c r="E25" s="7">
-        <v>101.5</v>
+        <v>108</v>
       </c>
       <c r="F25" s="8">
-        <v>-7.5</v>
+        <v>-1</v>
       </c>
       <c r="G25" s="8">
-        <v>-6.28</v>
+        <v>-0.89</v>
       </c>
       <c r="H25" s="9">
-        <v>5.4999999999999997E-3</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="10">
-        <v>155.30000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="I25" s="8">
+        <v>-100</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K25" s="9">
         <v>0.61</v>
@@ -2480,13 +2480,13 @@
         <v>10661.9</v>
       </c>
       <c r="M25" s="9">
-        <v>5.4999999999999997E-3</v>
-      </c>
-      <c r="N25" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O25" s="10">
-        <v>155.30000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="N25" s="8">
+        <v>-100</v>
+      </c>
+      <c r="O25" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P25" s="9">
         <v>0.61</v>
@@ -2497,84 +2497,84 @@
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B26" s="7">
-        <v>119</v>
+        <v>119.5</v>
       </c>
       <c r="C26" s="7">
+        <v>112</v>
+      </c>
+      <c r="D26" s="7">
         <v>119.5</v>
       </c>
-      <c r="D26" s="7">
-        <v>124.5</v>
-      </c>
       <c r="E26" s="7">
-        <v>109</v>
-      </c>
-      <c r="F26" s="10">
-        <v>2.5</v>
-      </c>
-      <c r="G26" s="10">
-        <v>2.14</v>
+        <v>101.5</v>
+      </c>
+      <c r="F26" s="8">
+        <v>-7.5</v>
+      </c>
+      <c r="G26" s="8">
+        <v>-6.28</v>
       </c>
       <c r="H26" s="9">
-        <v>0</v>
+        <v>5.4999999999999997E-3</v>
       </c>
       <c r="I26" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J26" s="9" t="s">
-        <v>17</v>
+      <c r="J26" s="10">
+        <v>155.30000000000001</v>
       </c>
       <c r="K26" s="9">
-        <v>0.60499999999999998</v>
+        <v>0.61</v>
       </c>
       <c r="L26" s="10">
-        <v>17176</v>
+        <v>10661.9</v>
       </c>
       <c r="M26" s="9">
-        <v>0</v>
+        <v>5.4999999999999997E-3</v>
       </c>
       <c r="N26" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O26" s="9" t="s">
-        <v>17</v>
+      <c r="O26" s="10">
+        <v>155.30000000000001</v>
       </c>
       <c r="P26" s="9">
-        <v>0.60499999999999998</v>
+        <v>0.61</v>
       </c>
       <c r="Q26" s="10">
-        <v>17176</v>
+        <v>10661.9</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B27" s="7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C27" s="7">
-        <v>117</v>
+        <v>119.5</v>
       </c>
       <c r="D27" s="7">
-        <v>151</v>
+        <v>124.5</v>
       </c>
       <c r="E27" s="7">
-        <v>111.5</v>
+        <v>109</v>
       </c>
       <c r="F27" s="10">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G27" s="10">
-        <v>0.86</v>
+        <v>2.14</v>
       </c>
       <c r="H27" s="9">
         <v>0</v>
       </c>
-      <c r="I27" s="8">
-        <v>-100</v>
+      <c r="I27" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J27" s="9" t="s">
         <v>17</v>
@@ -2588,8 +2588,8 @@
       <c r="M27" s="9">
         <v>0</v>
       </c>
-      <c r="N27" s="8">
-        <v>-100</v>
+      <c r="N27" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>17</v>
@@ -2603,34 +2603,34 @@
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B28" s="7">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C28" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D28" s="7">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="E28" s="7">
-        <v>105.5</v>
-      </c>
-      <c r="F28" s="8">
-        <v>-4.5</v>
-      </c>
-      <c r="G28" s="8">
-        <v>-3.73</v>
+        <v>111.5</v>
+      </c>
+      <c r="F28" s="10">
+        <v>1</v>
+      </c>
+      <c r="G28" s="10">
+        <v>0.86</v>
       </c>
       <c r="H28" s="9">
-        <v>2.7000000000000001E-3</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J28" s="10">
-        <v>96.3</v>
+        <v>0</v>
+      </c>
+      <c r="I28" s="8">
+        <v>-100</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K28" s="9">
         <v>0.60499999999999998</v>
@@ -2639,13 +2639,13 @@
         <v>17176</v>
       </c>
       <c r="M28" s="9">
-        <v>2.7000000000000001E-3</v>
-      </c>
-      <c r="N28" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O28" s="10">
-        <v>96.3</v>
+        <v>0</v>
+      </c>
+      <c r="N28" s="8">
+        <v>-100</v>
+      </c>
+      <c r="O28" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P28" s="9">
         <v>0.60499999999999998</v>
@@ -2656,84 +2656,84 @@
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B29" s="7">
-        <v>88.5</v>
+        <v>120</v>
       </c>
       <c r="C29" s="7">
-        <v>120.5</v>
+        <v>116</v>
       </c>
       <c r="D29" s="7">
-        <v>129.5</v>
+        <v>130</v>
       </c>
       <c r="E29" s="7">
-        <v>87.2</v>
-      </c>
-      <c r="F29" s="10">
-        <v>30.8</v>
-      </c>
-      <c r="G29" s="10">
-        <v>34.340000000000003</v>
+        <v>105.5</v>
+      </c>
+      <c r="F29" s="8">
+        <v>-4.5</v>
+      </c>
+      <c r="G29" s="8">
+        <v>-3.73</v>
       </c>
       <c r="H29" s="9">
-        <v>0</v>
-      </c>
-      <c r="I29" s="8">
-        <v>-100</v>
-      </c>
-      <c r="J29" s="9" t="s">
-        <v>17</v>
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="10">
+        <v>96.3</v>
       </c>
       <c r="K29" s="9">
-        <v>0.60199999999999998</v>
+        <v>0.60499999999999998</v>
       </c>
       <c r="L29" s="10">
-        <v>28030.400000000001</v>
+        <v>17176</v>
       </c>
       <c r="M29" s="9">
-        <v>0</v>
-      </c>
-      <c r="N29" s="8">
-        <v>-100</v>
-      </c>
-      <c r="O29" s="9" t="s">
-        <v>17</v>
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="N29" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O29" s="10">
+        <v>96.3</v>
       </c>
       <c r="P29" s="9">
-        <v>0.60199999999999998</v>
+        <v>0.60499999999999998</v>
       </c>
       <c r="Q29" s="10">
-        <v>28030.400000000001</v>
+        <v>17176</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B30" s="7">
-        <v>70</v>
+        <v>88.5</v>
       </c>
       <c r="C30" s="7">
-        <v>89.7</v>
+        <v>120.5</v>
       </c>
       <c r="D30" s="7">
-        <v>95</v>
+        <v>129.5</v>
       </c>
       <c r="E30" s="7">
-        <v>69.900000000000006</v>
+        <v>87.2</v>
       </c>
       <c r="F30" s="10">
-        <v>20.3</v>
+        <v>30.8</v>
       </c>
       <c r="G30" s="10">
-        <v>29.25</v>
+        <v>34.340000000000003</v>
       </c>
       <c r="H30" s="9">
-        <v>0.59899999999999998</v>
-      </c>
-      <c r="I30" s="10">
-        <v>21376.7</v>
+        <v>0</v>
+      </c>
+      <c r="I30" s="8">
+        <v>-100</v>
       </c>
       <c r="J30" s="9" t="s">
         <v>17</v>
@@ -2745,10 +2745,10 @@
         <v>28030.400000000001</v>
       </c>
       <c r="M30" s="9">
-        <v>0.59899999999999998</v>
-      </c>
-      <c r="N30" s="10">
-        <v>21376.7</v>
+        <v>0</v>
+      </c>
+      <c r="N30" s="8">
+        <v>-100</v>
       </c>
       <c r="O30" s="9" t="s">
         <v>17</v>
@@ -2762,137 +2762,137 @@
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B31" s="7">
-        <v>108.5</v>
+        <v>70</v>
       </c>
       <c r="C31" s="7">
-        <v>69.400000000000006</v>
+        <v>89.7</v>
       </c>
       <c r="D31" s="7">
-        <v>112.5</v>
+        <v>95</v>
       </c>
       <c r="E31" s="7">
-        <v>58.6</v>
-      </c>
-      <c r="F31" s="8">
-        <v>-44.6</v>
-      </c>
-      <c r="G31" s="8">
-        <v>-39.119999999999997</v>
+        <v>69.900000000000006</v>
+      </c>
+      <c r="F31" s="10">
+        <v>20.3</v>
+      </c>
+      <c r="G31" s="10">
+        <v>29.25</v>
       </c>
       <c r="H31" s="9">
-        <v>2.8E-3</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="10">
-        <v>30.4</v>
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="I31" s="10">
+        <v>21376.7</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K31" s="9">
-        <v>2.8E-3</v>
+        <v>0.60199999999999998</v>
       </c>
       <c r="L31" s="10">
-        <v>30.4</v>
+        <v>28030.400000000001</v>
       </c>
       <c r="M31" s="9">
-        <v>2.8E-3</v>
-      </c>
-      <c r="N31" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O31" s="10">
-        <v>30.4</v>
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="N31" s="10">
+        <v>21376.7</v>
+      </c>
+      <c r="O31" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P31" s="9">
-        <v>2.8E-3</v>
+        <v>0.60199999999999998</v>
       </c>
       <c r="Q31" s="10">
-        <v>30.4</v>
+        <v>28030.400000000001</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B32" s="7">
-        <v>121.5</v>
+        <v>108.5</v>
       </c>
       <c r="C32" s="7">
-        <v>114</v>
+        <v>69.400000000000006</v>
       </c>
       <c r="D32" s="7">
-        <v>128.5</v>
+        <v>112.5</v>
       </c>
       <c r="E32" s="7">
-        <v>114</v>
+        <v>58.6</v>
       </c>
       <c r="F32" s="8">
-        <v>-9</v>
+        <v>-44.6</v>
       </c>
       <c r="G32" s="8">
-        <v>-7.32</v>
+        <v>-39.119999999999997</v>
       </c>
       <c r="H32" s="9">
-        <v>0</v>
+        <v>2.8E-3</v>
       </c>
       <c r="I32" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J32" s="9" t="s">
-        <v>17</v>
+      <c r="J32" s="10">
+        <v>30.4</v>
       </c>
       <c r="K32" s="9">
-        <v>0</v>
-      </c>
-      <c r="L32" s="9" t="s">
-        <v>17</v>
+        <v>2.8E-3</v>
+      </c>
+      <c r="L32" s="10">
+        <v>30.4</v>
       </c>
       <c r="M32" s="9">
-        <v>0</v>
+        <v>2.8E-3</v>
       </c>
       <c r="N32" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O32" s="9" t="s">
-        <v>17</v>
+      <c r="O32" s="10">
+        <v>30.4</v>
       </c>
       <c r="P32" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="9" t="s">
-        <v>17</v>
+        <v>2.8E-3</v>
+      </c>
+      <c r="Q32" s="10">
+        <v>30.4</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B33" s="7">
-        <v>129.5</v>
+        <v>121.5</v>
       </c>
       <c r="C33" s="7">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D33" s="7">
-        <v>134</v>
+        <v>128.5</v>
       </c>
       <c r="E33" s="7">
-        <v>119.5</v>
+        <v>114</v>
       </c>
       <c r="F33" s="8">
         <v>-9</v>
       </c>
       <c r="G33" s="8">
-        <v>-6.82</v>
+        <v>-7.32</v>
       </c>
       <c r="H33" s="9">
         <v>0</v>
       </c>
-      <c r="I33" s="8">
-        <v>-100</v>
+      <c r="I33" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J33" s="9" t="s">
         <v>17</v>
@@ -2906,8 +2906,8 @@
       <c r="M33" s="9">
         <v>0</v>
       </c>
-      <c r="N33" s="8">
-        <v>-100</v>
+      <c r="N33" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>17</v>
@@ -2921,137 +2921,137 @@
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43800</v>
+        <v>43831</v>
       </c>
       <c r="B34" s="7">
-        <v>141.5</v>
+        <v>129.5</v>
       </c>
       <c r="C34" s="7">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D34" s="7">
-        <v>142.5</v>
+        <v>134</v>
       </c>
       <c r="E34" s="7">
-        <v>127.5</v>
+        <v>119.5</v>
       </c>
       <c r="F34" s="8">
-        <v>-9.5</v>
+        <v>-9</v>
       </c>
       <c r="G34" s="8">
-        <v>-6.71</v>
+        <v>-6.82</v>
       </c>
       <c r="H34" s="9">
-        <v>3.0999999999999999E-3</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="10">
-        <v>10.1</v>
+        <v>0</v>
+      </c>
+      <c r="I34" s="8">
+        <v>-100</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K34" s="9">
-        <v>8.6999999999999994E-3</v>
-      </c>
-      <c r="L34" s="8">
-        <v>-93.5</v>
+        <v>0</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M34" s="9">
-        <v>3.0999999999999999E-3</v>
-      </c>
-      <c r="N34" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O34" s="10">
-        <v>10.1</v>
+        <v>0</v>
+      </c>
+      <c r="N34" s="8">
+        <v>-100</v>
+      </c>
+      <c r="O34" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P34" s="9">
-        <v>8.6999999999999994E-3</v>
-      </c>
-      <c r="Q34" s="8">
-        <v>-93.5</v>
+        <v>0</v>
+      </c>
+      <c r="Q34" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="B35" s="7">
-        <v>133.5</v>
+        <v>141.5</v>
       </c>
       <c r="C35" s="7">
-        <v>141.5</v>
+        <v>132</v>
       </c>
       <c r="D35" s="7">
-        <v>146</v>
+        <v>142.5</v>
       </c>
       <c r="E35" s="7">
-        <v>128</v>
-      </c>
-      <c r="F35" s="10">
-        <v>8</v>
-      </c>
-      <c r="G35" s="10">
-        <v>5.99</v>
+        <v>127.5</v>
+      </c>
+      <c r="F35" s="8">
+        <v>-9.5</v>
+      </c>
+      <c r="G35" s="8">
+        <v>-6.71</v>
       </c>
       <c r="H35" s="9">
-        <v>0</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="I35" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J35" s="9" t="s">
-        <v>17</v>
+      <c r="J35" s="10">
+        <v>10.1</v>
       </c>
       <c r="K35" s="9">
-        <v>5.7000000000000002E-3</v>
+        <v>8.6999999999999994E-3</v>
       </c>
       <c r="L35" s="8">
-        <v>-95.6</v>
+        <v>-93.5</v>
       </c>
       <c r="M35" s="9">
-        <v>0</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="N35" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O35" s="9" t="s">
-        <v>17</v>
+      <c r="O35" s="10">
+        <v>10.1</v>
       </c>
       <c r="P35" s="9">
-        <v>5.7000000000000002E-3</v>
+        <v>8.6999999999999994E-3</v>
       </c>
       <c r="Q35" s="8">
-        <v>-95.6</v>
+        <v>-93.5</v>
       </c>
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B36" s="7">
-        <v>140</v>
+        <v>133.5</v>
       </c>
       <c r="C36" s="7">
-        <v>133.5</v>
+        <v>141.5</v>
       </c>
       <c r="D36" s="7">
-        <v>145.5</v>
+        <v>146</v>
       </c>
       <c r="E36" s="7">
-        <v>132</v>
-      </c>
-      <c r="F36" s="8">
-        <v>-6</v>
-      </c>
-      <c r="G36" s="8">
-        <v>-4.3</v>
+        <v>128</v>
+      </c>
+      <c r="F36" s="10">
+        <v>8</v>
+      </c>
+      <c r="G36" s="10">
+        <v>5.99</v>
       </c>
       <c r="H36" s="9">
         <v>0</v>
       </c>
-      <c r="I36" s="8">
-        <v>-100</v>
+      <c r="I36" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J36" s="9" t="s">
         <v>17</v>
@@ -3065,8 +3065,8 @@
       <c r="M36" s="9">
         <v>0</v>
       </c>
-      <c r="N36" s="8">
-        <v>-100</v>
+      <c r="N36" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O36" s="9" t="s">
         <v>17</v>
@@ -3080,34 +3080,34 @@
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="B37" s="7">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C37" s="7">
-        <v>139.5</v>
+        <v>133.5</v>
       </c>
       <c r="D37" s="7">
-        <v>149</v>
+        <v>145.5</v>
       </c>
       <c r="E37" s="7">
-        <v>139.5</v>
-      </c>
-      <c r="F37" s="9">
-        <v>0</v>
-      </c>
-      <c r="G37" s="9">
-        <v>0</v>
+        <v>132</v>
+      </c>
+      <c r="F37" s="8">
+        <v>-6</v>
+      </c>
+      <c r="G37" s="8">
+        <v>-4.3</v>
       </c>
       <c r="H37" s="9">
-        <v>2.2000000000000001E-3</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J37" s="8">
-        <v>-31.1</v>
+        <v>0</v>
+      </c>
+      <c r="I37" s="8">
+        <v>-100</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K37" s="9">
         <v>5.7000000000000002E-3</v>
@@ -3116,13 +3116,13 @@
         <v>-95.6</v>
       </c>
       <c r="M37" s="9">
-        <v>2.2000000000000001E-3</v>
-      </c>
-      <c r="N37" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O37" s="8">
-        <v>-31.1</v>
+        <v>0</v>
+      </c>
+      <c r="N37" s="8">
+        <v>-100</v>
+      </c>
+      <c r="O37" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P37" s="9">
         <v>5.7000000000000002E-3</v>
@@ -3133,84 +3133,84 @@
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="B38" s="7">
-        <v>149.5</v>
+        <v>142</v>
       </c>
       <c r="C38" s="7">
         <v>139.5</v>
       </c>
       <c r="D38" s="7">
-        <v>151.5</v>
+        <v>149</v>
       </c>
       <c r="E38" s="7">
-        <v>136</v>
-      </c>
-      <c r="F38" s="8">
-        <v>-11</v>
-      </c>
-      <c r="G38" s="8">
-        <v>-7.31</v>
+        <v>139.5</v>
+      </c>
+      <c r="F38" s="9">
+        <v>0</v>
+      </c>
+      <c r="G38" s="9">
+        <v>0</v>
       </c>
       <c r="H38" s="9">
-        <v>0</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="I38" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J38" s="9" t="s">
-        <v>17</v>
+      <c r="J38" s="8">
+        <v>-31.1</v>
       </c>
       <c r="K38" s="9">
-        <v>3.5000000000000001E-3</v>
+        <v>5.7000000000000002E-3</v>
       </c>
       <c r="L38" s="8">
-        <v>-97.2</v>
+        <v>-95.6</v>
       </c>
       <c r="M38" s="9">
-        <v>0</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="N38" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O38" s="9" t="s">
-        <v>17</v>
+      <c r="O38" s="8">
+        <v>-31.1</v>
       </c>
       <c r="P38" s="9">
-        <v>3.5000000000000001E-3</v>
+        <v>5.7000000000000002E-3</v>
       </c>
       <c r="Q38" s="8">
-        <v>-97.2</v>
+        <v>-95.6</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="B39" s="7">
-        <v>165.5</v>
+        <v>149.5</v>
       </c>
       <c r="C39" s="7">
-        <v>150.5</v>
+        <v>139.5</v>
       </c>
       <c r="D39" s="7">
-        <v>170</v>
+        <v>151.5</v>
       </c>
       <c r="E39" s="7">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="F39" s="8">
-        <v>-14.5</v>
+        <v>-11</v>
       </c>
       <c r="G39" s="8">
-        <v>-8.7899999999999991</v>
+        <v>-7.31</v>
       </c>
       <c r="H39" s="9">
         <v>0</v>
       </c>
-      <c r="I39" s="8">
-        <v>-100</v>
+      <c r="I39" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J39" s="9" t="s">
         <v>17</v>
@@ -3224,8 +3224,8 @@
       <c r="M39" s="9">
         <v>0</v>
       </c>
-      <c r="N39" s="8">
-        <v>-100</v>
+      <c r="N39" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>17</v>
@@ -3239,34 +3239,34 @@
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>43617</v>
+        <v>43647</v>
       </c>
       <c r="B40" s="7">
-        <v>141</v>
+        <v>165.5</v>
       </c>
       <c r="C40" s="7">
-        <v>165</v>
+        <v>150.5</v>
       </c>
       <c r="D40" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E40" s="7">
-        <v>140</v>
-      </c>
-      <c r="F40" s="10">
-        <v>23</v>
-      </c>
-      <c r="G40" s="10">
-        <v>16.2</v>
+        <v>149</v>
+      </c>
+      <c r="F40" s="8">
+        <v>-14.5</v>
+      </c>
+      <c r="G40" s="8">
+        <v>-8.7899999999999991</v>
       </c>
       <c r="H40" s="9">
-        <v>1.4E-3</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J40" s="8">
-        <v>-13.4</v>
+        <v>0</v>
+      </c>
+      <c r="I40" s="8">
+        <v>-100</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K40" s="9">
         <v>3.5000000000000001E-3</v>
@@ -3275,13 +3275,13 @@
         <v>-97.2</v>
       </c>
       <c r="M40" s="9">
-        <v>1.4E-3</v>
-      </c>
-      <c r="N40" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O40" s="8">
-        <v>-13.4</v>
+        <v>0</v>
+      </c>
+      <c r="N40" s="8">
+        <v>-100</v>
+      </c>
+      <c r="O40" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P40" s="9">
         <v>3.5000000000000001E-3</v>
@@ -3292,87 +3292,87 @@
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>43586</v>
+        <v>43617</v>
       </c>
       <c r="B41" s="7">
-        <v>155.5</v>
+        <v>141</v>
       </c>
       <c r="C41" s="7">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="D41" s="7">
-        <v>157.5</v>
+        <v>168</v>
       </c>
       <c r="E41" s="7">
-        <v>138</v>
-      </c>
-      <c r="F41" s="8">
-        <v>-13.5</v>
-      </c>
-      <c r="G41" s="8">
-        <v>-8.68</v>
+        <v>140</v>
+      </c>
+      <c r="F41" s="10">
+        <v>23</v>
+      </c>
+      <c r="G41" s="10">
+        <v>16.2</v>
       </c>
       <c r="H41" s="9">
-        <v>0</v>
+        <v>1.4E-3</v>
       </c>
       <c r="I41" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J41" s="9" t="s">
-        <v>17</v>
+      <c r="J41" s="8">
+        <v>-13.4</v>
       </c>
       <c r="K41" s="9">
-        <v>2.0999999999999999E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="L41" s="8">
-        <v>-98.3</v>
+        <v>-97.2</v>
       </c>
       <c r="M41" s="9">
-        <v>0</v>
+        <v>1.4E-3</v>
       </c>
       <c r="N41" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O41" s="9" t="s">
-        <v>17</v>
+      <c r="O41" s="8">
+        <v>-13.4</v>
       </c>
       <c r="P41" s="9">
-        <v>2.0999999999999999E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="Q41" s="8">
-        <v>-98.3</v>
+        <v>-97.2</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>43556</v>
+        <v>43586</v>
       </c>
       <c r="B42" s="7">
-        <v>168</v>
+        <v>155.5</v>
       </c>
       <c r="C42" s="7">
-        <v>155.5</v>
+        <v>142</v>
       </c>
       <c r="D42" s="7">
-        <v>168.5</v>
+        <v>157.5</v>
       </c>
       <c r="E42" s="7">
-        <v>151.5</v>
+        <v>138</v>
       </c>
       <c r="F42" s="8">
         <v>-13.5</v>
       </c>
       <c r="G42" s="8">
-        <v>-7.99</v>
+        <v>-8.68</v>
       </c>
       <c r="H42" s="9">
         <v>0</v>
       </c>
-      <c r="I42" s="8">
-        <v>-100</v>
-      </c>
-      <c r="J42" s="8">
-        <v>-100</v>
+      <c r="I42" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K42" s="9">
         <v>2.0999999999999999E-3</v>
@@ -3383,11 +3383,11 @@
       <c r="M42" s="9">
         <v>0</v>
       </c>
-      <c r="N42" s="8">
-        <v>-100</v>
-      </c>
-      <c r="O42" s="8">
-        <v>-100</v>
+      <c r="N42" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O42" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P42" s="9">
         <v>2.0999999999999999E-3</v>
@@ -3398,34 +3398,34 @@
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B43" s="7">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="C43" s="7">
-        <v>169</v>
+        <v>155.5</v>
       </c>
       <c r="D43" s="7">
-        <v>185.5</v>
+        <v>168.5</v>
       </c>
       <c r="E43" s="7">
-        <v>157.5</v>
+        <v>151.5</v>
       </c>
       <c r="F43" s="8">
-        <v>-11</v>
+        <v>-13.5</v>
       </c>
       <c r="G43" s="8">
-        <v>-6.11</v>
+        <v>-7.99</v>
       </c>
       <c r="H43" s="9">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I43" s="8">
+        <v>-100</v>
       </c>
       <c r="J43" s="8">
-        <v>-95.4</v>
+        <v>-100</v>
       </c>
       <c r="K43" s="9">
         <v>2.0999999999999999E-3</v>
@@ -3434,13 +3434,13 @@
         <v>-98.3</v>
       </c>
       <c r="M43" s="9">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="N43" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N43" s="8">
+        <v>-100</v>
       </c>
       <c r="O43" s="8">
-        <v>-95.4</v>
+        <v>-100</v>
       </c>
       <c r="P43" s="9">
         <v>2.0999999999999999E-3</v>
@@ -3451,84 +3451,84 @@
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B44" s="7">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C44" s="7">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="D44" s="7">
-        <v>191</v>
+        <v>185.5</v>
       </c>
       <c r="E44" s="7">
-        <v>177</v>
-      </c>
-      <c r="F44" s="9">
-        <v>0</v>
-      </c>
-      <c r="G44" s="9">
-        <v>0</v>
+        <v>157.5</v>
+      </c>
+      <c r="F44" s="8">
+        <v>-11</v>
+      </c>
+      <c r="G44" s="8">
+        <v>-6.11</v>
       </c>
       <c r="H44" s="9">
-        <v>0</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="I44" s="9" t="s">
         <v>17</v>
       </c>
       <c r="J44" s="8">
-        <v>-100</v>
+        <v>-95.4</v>
       </c>
       <c r="K44" s="9">
-        <v>0</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="L44" s="8">
-        <v>-100</v>
+        <v>-98.3</v>
       </c>
       <c r="M44" s="9">
-        <v>0</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="N44" s="9" t="s">
         <v>17</v>
       </c>
       <c r="O44" s="8">
-        <v>-100</v>
+        <v>-95.4</v>
       </c>
       <c r="P44" s="9">
-        <v>0</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="Q44" s="8">
-        <v>-100</v>
+        <v>-98.3</v>
       </c>
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B45" s="7">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="C45" s="7">
         <v>180</v>
       </c>
       <c r="D45" s="7">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E45" s="7">
-        <v>152.5</v>
-      </c>
-      <c r="F45" s="10">
-        <v>23.5</v>
-      </c>
-      <c r="G45" s="10">
-        <v>15.02</v>
+        <v>177</v>
+      </c>
+      <c r="F45" s="9">
+        <v>0</v>
+      </c>
+      <c r="G45" s="9">
+        <v>0</v>
       </c>
       <c r="H45" s="9">
         <v>0</v>
       </c>
-      <c r="I45" s="8">
-        <v>-100</v>
+      <c r="I45" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J45" s="8">
         <v>-100</v>
@@ -3542,8 +3542,8 @@
       <c r="M45" s="9">
         <v>0</v>
       </c>
-      <c r="N45" s="8">
-        <v>-100</v>
+      <c r="N45" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O45" s="8">
         <v>-100</v>
@@ -3557,190 +3557,190 @@
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B46" s="7">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="C46" s="7">
-        <v>156.5</v>
+        <v>180</v>
       </c>
       <c r="D46" s="7">
-        <v>164.5</v>
+        <v>192</v>
       </c>
       <c r="E46" s="7">
-        <v>133.5</v>
+        <v>152.5</v>
       </c>
       <c r="F46" s="10">
-        <v>10.5</v>
+        <v>23.5</v>
       </c>
       <c r="G46" s="10">
-        <v>7.19</v>
+        <v>15.02</v>
       </c>
       <c r="H46" s="9">
-        <v>2.8E-3</v>
-      </c>
-      <c r="I46" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I46" s="8">
+        <v>-100</v>
+      </c>
+      <c r="J46" s="8">
+        <v>-100</v>
       </c>
       <c r="K46" s="9">
-        <v>0.13300000000000001</v>
-      </c>
-      <c r="L46" s="10">
-        <v>3447.6</v>
+        <v>0</v>
+      </c>
+      <c r="L46" s="8">
+        <v>-100</v>
       </c>
       <c r="M46" s="9">
-        <v>2.8E-3</v>
-      </c>
-      <c r="N46" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O46" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N46" s="8">
+        <v>-100</v>
+      </c>
+      <c r="O46" s="8">
+        <v>-100</v>
       </c>
       <c r="P46" s="9">
-        <v>0.13300000000000001</v>
-      </c>
-      <c r="Q46" s="10">
-        <v>3447.6</v>
+        <v>0</v>
+      </c>
+      <c r="Q46" s="8">
+        <v>-100</v>
       </c>
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B47" s="7">
-        <v>122.5</v>
+        <v>143</v>
       </c>
       <c r="C47" s="7">
-        <v>146</v>
+        <v>156.5</v>
       </c>
       <c r="D47" s="7">
-        <v>149</v>
+        <v>164.5</v>
       </c>
       <c r="E47" s="7">
-        <v>118</v>
+        <v>133.5</v>
       </c>
       <c r="F47" s="10">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="G47" s="10">
-        <v>20.66</v>
+        <v>7.19</v>
       </c>
       <c r="H47" s="9">
-        <v>0</v>
+        <v>2.8E-3</v>
       </c>
       <c r="I47" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J47" s="8">
-        <v>-100</v>
+      <c r="J47" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K47" s="9">
-        <v>0.13100000000000001</v>
+        <v>0.13300000000000001</v>
       </c>
       <c r="L47" s="10">
-        <v>3373.9</v>
+        <v>3447.6</v>
       </c>
       <c r="M47" s="9">
-        <v>0</v>
+        <v>2.8E-3</v>
       </c>
       <c r="N47" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O47" s="8">
-        <v>-100</v>
+      <c r="O47" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P47" s="9">
-        <v>0.13100000000000001</v>
+        <v>0.13300000000000001</v>
       </c>
       <c r="Q47" s="10">
-        <v>3373.9</v>
+        <v>3447.6</v>
       </c>
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>43374</v>
+        <v>43405</v>
       </c>
       <c r="B48" s="7">
-        <v>149.5</v>
+        <v>122.5</v>
       </c>
       <c r="C48" s="7">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="D48" s="7">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E48" s="7">
-        <v>119.5</v>
-      </c>
-      <c r="F48" s="8">
-        <v>-24.5</v>
-      </c>
-      <c r="G48" s="8">
-        <v>-16.84</v>
+        <v>118</v>
+      </c>
+      <c r="F48" s="10">
+        <v>25</v>
+      </c>
+      <c r="G48" s="10">
+        <v>20.66</v>
       </c>
       <c r="H48" s="9">
         <v>0</v>
       </c>
-      <c r="I48" s="8">
+      <c r="I48" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" s="8">
         <v>-100</v>
-      </c>
-      <c r="J48" s="9" t="s">
-        <v>17</v>
       </c>
       <c r="K48" s="9">
         <v>0.13100000000000001</v>
       </c>
       <c r="L48" s="10">
-        <v>3468.8</v>
+        <v>3373.9</v>
       </c>
       <c r="M48" s="9">
         <v>0</v>
       </c>
-      <c r="N48" s="8">
+      <c r="N48" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O48" s="8">
         <v>-100</v>
-      </c>
-      <c r="O48" s="9" t="s">
-        <v>17</v>
       </c>
       <c r="P48" s="9">
         <v>0.13100000000000001</v>
       </c>
       <c r="Q48" s="10">
-        <v>3468.8</v>
+        <v>3373.9</v>
       </c>
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>43344</v>
+        <v>43374</v>
       </c>
       <c r="B49" s="7">
-        <v>146</v>
+        <v>149.5</v>
       </c>
       <c r="C49" s="7">
-        <v>145.5</v>
+        <v>121</v>
       </c>
       <c r="D49" s="7">
-        <v>149.5</v>
+        <v>157</v>
       </c>
       <c r="E49" s="7">
-        <v>118</v>
-      </c>
-      <c r="F49" s="10">
-        <v>2</v>
-      </c>
-      <c r="G49" s="10">
-        <v>1.39</v>
+        <v>119.5</v>
+      </c>
+      <c r="F49" s="8">
+        <v>-24.5</v>
+      </c>
+      <c r="G49" s="8">
+        <v>-16.84</v>
       </c>
       <c r="H49" s="9">
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="I49" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I49" s="8">
+        <v>-100</v>
       </c>
       <c r="J49" s="9" t="s">
         <v>17</v>
@@ -3752,10 +3752,10 @@
         <v>3468.8</v>
       </c>
       <c r="M49" s="9">
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="N49" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N49" s="8">
+        <v>-100</v>
       </c>
       <c r="O49" s="9" t="s">
         <v>17</v>
@@ -3769,28 +3769,28 @@
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>43313</v>
+        <v>43344</v>
       </c>
       <c r="B50" s="7">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="C50" s="7">
-        <v>143.5</v>
+        <v>145.5</v>
       </c>
       <c r="D50" s="7">
-        <v>158</v>
+        <v>149.5</v>
       </c>
       <c r="E50" s="7">
-        <v>139.5</v>
-      </c>
-      <c r="F50" s="8">
-        <v>-13</v>
-      </c>
-      <c r="G50" s="8">
-        <v>-8.31</v>
+        <v>118</v>
+      </c>
+      <c r="F50" s="10">
+        <v>2</v>
+      </c>
+      <c r="G50" s="10">
+        <v>1.39</v>
       </c>
       <c r="H50" s="9">
-        <v>0</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="I50" s="9" t="s">
         <v>17</v>
@@ -3799,13 +3799,13 @@
         <v>17</v>
       </c>
       <c r="K50" s="9">
-        <v>0.127</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="L50" s="10">
-        <v>3382.8</v>
+        <v>3468.8</v>
       </c>
       <c r="M50" s="9">
-        <v>0</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="N50" s="9" t="s">
         <v>17</v>
@@ -3814,39 +3814,39 @@
         <v>17</v>
       </c>
       <c r="P50" s="9">
-        <v>0.127</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="Q50" s="10">
-        <v>3382.8</v>
+        <v>3468.8</v>
       </c>
     </row>
     <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>43282</v>
+        <v>43313</v>
       </c>
       <c r="B51" s="7">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C51" s="7">
-        <v>156.5</v>
+        <v>143.5</v>
       </c>
       <c r="D51" s="7">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E51" s="7">
-        <v>147.5</v>
-      </c>
-      <c r="F51" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="G51" s="10">
-        <v>0.32</v>
+        <v>139.5</v>
+      </c>
+      <c r="F51" s="8">
+        <v>-13</v>
+      </c>
+      <c r="G51" s="8">
+        <v>-8.31</v>
       </c>
       <c r="H51" s="9">
         <v>0</v>
       </c>
-      <c r="I51" s="8">
-        <v>-100</v>
+      <c r="I51" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J51" s="9" t="s">
         <v>17</v>
@@ -3860,8 +3860,8 @@
       <c r="M51" s="9">
         <v>0</v>
       </c>
-      <c r="N51" s="8">
-        <v>-100</v>
+      <c r="N51" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>17</v>
@@ -3875,31 +3875,31 @@
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>43252</v>
+        <v>43282</v>
       </c>
       <c r="B52" s="7">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="C52" s="7">
-        <v>156</v>
+        <v>156.5</v>
       </c>
       <c r="D52" s="7">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="E52" s="7">
-        <v>152</v>
-      </c>
-      <c r="F52" s="8">
-        <v>-6</v>
-      </c>
-      <c r="G52" s="8">
-        <v>-3.7</v>
+        <v>147.5</v>
+      </c>
+      <c r="F52" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="G52" s="10">
+        <v>0.32</v>
       </c>
       <c r="H52" s="9">
-        <v>1.6000000000000001E-3</v>
-      </c>
-      <c r="I52" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I52" s="8">
+        <v>-100</v>
       </c>
       <c r="J52" s="9" t="s">
         <v>17</v>
@@ -3911,10 +3911,10 @@
         <v>3382.8</v>
       </c>
       <c r="M52" s="9">
-        <v>1.6000000000000001E-3</v>
-      </c>
-      <c r="N52" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N52" s="8">
+        <v>-100</v>
       </c>
       <c r="O52" s="9" t="s">
         <v>17</v>
@@ -3928,158 +3928,158 @@
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>43221</v>
+        <v>43252</v>
       </c>
       <c r="B53" s="7">
-        <v>168.5</v>
+        <v>178</v>
       </c>
       <c r="C53" s="7">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D53" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E53" s="7">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F53" s="8">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="G53" s="8">
-        <v>-4.1399999999999997</v>
+        <v>-3.7</v>
       </c>
       <c r="H53" s="9">
-        <v>0</v>
-      </c>
-      <c r="I53" s="8">
-        <v>-100</v>
-      </c>
-      <c r="J53" s="8">
-        <v>-100</v>
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J53" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K53" s="9">
-        <v>0.126</v>
+        <v>0.127</v>
       </c>
       <c r="L53" s="10">
-        <v>3339.9</v>
+        <v>3382.8</v>
       </c>
       <c r="M53" s="9">
-        <v>0</v>
-      </c>
-      <c r="N53" s="8">
-        <v>-100</v>
-      </c>
-      <c r="O53" s="8">
-        <v>-100</v>
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="N53" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O53" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P53" s="9">
-        <v>0.126</v>
+        <v>0.127</v>
       </c>
       <c r="Q53" s="10">
-        <v>3339.9</v>
+        <v>3382.8</v>
       </c>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>43191</v>
+        <v>43221</v>
       </c>
       <c r="B54" s="7">
-        <v>184</v>
+        <v>168.5</v>
       </c>
       <c r="C54" s="7">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D54" s="7">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E54" s="7">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="F54" s="8">
-        <v>-13</v>
+        <v>-7</v>
       </c>
       <c r="G54" s="8">
-        <v>-7.14</v>
+        <v>-4.1399999999999997</v>
       </c>
       <c r="H54" s="9">
-        <v>2.3999999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="I54" s="8">
-        <v>-94.9</v>
-      </c>
-      <c r="J54" s="9" t="s">
-        <v>17</v>
+        <v>-100</v>
+      </c>
+      <c r="J54" s="8">
+        <v>-100</v>
       </c>
       <c r="K54" s="9">
         <v>0.126</v>
       </c>
-      <c r="L54" s="9" t="s">
-        <v>17</v>
+      <c r="L54" s="10">
+        <v>3339.9</v>
       </c>
       <c r="M54" s="9">
-        <v>2.3999999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="N54" s="8">
-        <v>-94.9</v>
-      </c>
-      <c r="O54" s="9" t="s">
-        <v>17</v>
+        <v>-100</v>
+      </c>
+      <c r="O54" s="8">
+        <v>-100</v>
       </c>
       <c r="P54" s="9">
         <v>0.126</v>
       </c>
-      <c r="Q54" s="9" t="s">
-        <v>17</v>
+      <c r="Q54" s="10">
+        <v>3339.9</v>
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>43160</v>
+        <v>43191</v>
       </c>
       <c r="B55" s="7">
+        <v>184</v>
+      </c>
+      <c r="C55" s="7">
         <v>169</v>
       </c>
-      <c r="C55" s="7">
-        <v>182</v>
-      </c>
       <c r="D55" s="7">
-        <v>189.5</v>
+        <v>192</v>
       </c>
       <c r="E55" s="7">
-        <v>167</v>
-      </c>
-      <c r="F55" s="10">
-        <v>11</v>
-      </c>
-      <c r="G55" s="10">
-        <v>6.43</v>
+        <v>161</v>
+      </c>
+      <c r="F55" s="8">
+        <v>-13</v>
+      </c>
+      <c r="G55" s="8">
+        <v>-7.14</v>
       </c>
       <c r="H55" s="9">
-        <v>4.65E-2</v>
-      </c>
-      <c r="I55" s="10">
-        <v>1251.7</v>
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="I55" s="8">
+        <v>-94.9</v>
       </c>
       <c r="J55" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K55" s="9">
-        <v>0.124</v>
+        <v>0.126</v>
       </c>
       <c r="L55" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M55" s="9">
-        <v>4.65E-2</v>
-      </c>
-      <c r="N55" s="10">
-        <v>1251.7</v>
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="N55" s="8">
+        <v>-94.9</v>
       </c>
       <c r="O55" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P55" s="9">
-        <v>0.124</v>
+        <v>0.126</v>
       </c>
       <c r="Q55" s="9" t="s">
         <v>17</v>
@@ -4087,52 +4087,52 @@
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
-        <v>43132</v>
+        <v>43160</v>
       </c>
       <c r="B56" s="7">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="C56" s="7">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="D56" s="7">
         <v>189.5</v>
       </c>
       <c r="E56" s="7">
-        <v>152</v>
-      </c>
-      <c r="F56" s="8">
-        <v>-14</v>
-      </c>
-      <c r="G56" s="8">
-        <v>-7.57</v>
+        <v>167</v>
+      </c>
+      <c r="F56" s="10">
+        <v>11</v>
+      </c>
+      <c r="G56" s="10">
+        <v>6.43</v>
       </c>
       <c r="H56" s="9">
-        <v>3.3999999999999998E-3</v>
-      </c>
-      <c r="I56" s="8">
-        <v>-95.3</v>
+        <v>4.65E-2</v>
+      </c>
+      <c r="I56" s="10">
+        <v>1251.7</v>
       </c>
       <c r="J56" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K56" s="9">
-        <v>7.6999999999999999E-2</v>
+        <v>0.124</v>
       </c>
       <c r="L56" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M56" s="9">
-        <v>3.3999999999999998E-3</v>
-      </c>
-      <c r="N56" s="8">
-        <v>-95.3</v>
+        <v>4.65E-2</v>
+      </c>
+      <c r="N56" s="10">
+        <v>1251.7</v>
       </c>
       <c r="O56" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P56" s="9">
-        <v>7.6999999999999999E-2</v>
+        <v>0.124</v>
       </c>
       <c r="Q56" s="9" t="s">
         <v>17</v>
@@ -4140,52 +4140,52 @@
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
-        <v>43101</v>
+        <v>43132</v>
       </c>
       <c r="B57" s="7">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="C57" s="7">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="D57" s="7">
-        <v>196.5</v>
+        <v>189.5</v>
       </c>
       <c r="E57" s="7">
-        <v>148</v>
-      </c>
-      <c r="F57" s="10">
-        <v>34.5</v>
-      </c>
-      <c r="G57" s="10">
-        <v>22.92</v>
+        <v>152</v>
+      </c>
+      <c r="F57" s="8">
+        <v>-14</v>
+      </c>
+      <c r="G57" s="8">
+        <v>-7.57</v>
       </c>
       <c r="H57" s="9">
-        <v>7.3599999999999999E-2</v>
-      </c>
-      <c r="I57" s="9" t="s">
-        <v>17</v>
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="I57" s="8">
+        <v>-95.3</v>
       </c>
       <c r="J57" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K57" s="9">
-        <v>7.3599999999999999E-2</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="L57" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M57" s="9">
-        <v>7.3599999999999999E-2</v>
-      </c>
-      <c r="N57" s="9" t="s">
-        <v>17</v>
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="N57" s="8">
+        <v>-95.3</v>
       </c>
       <c r="O57" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P57" s="9">
-        <v>7.3599999999999999E-2</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="Q57" s="9" t="s">
         <v>17</v>
@@ -4193,87 +4193,87 @@
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
-        <v>43070</v>
+        <v>43101</v>
       </c>
       <c r="B58" s="7">
-        <v>152.5</v>
+        <v>151</v>
       </c>
       <c r="C58" s="7">
-        <v>150.5</v>
+        <v>185</v>
       </c>
       <c r="D58" s="7">
-        <v>156</v>
+        <v>196.5</v>
       </c>
       <c r="E58" s="7">
-        <v>135</v>
-      </c>
-      <c r="F58" s="8">
-        <v>-1</v>
-      </c>
-      <c r="G58" s="8">
-        <v>-0.66</v>
+        <v>148</v>
+      </c>
+      <c r="F58" s="10">
+        <v>34.5</v>
+      </c>
+      <c r="G58" s="10">
+        <v>22.92</v>
       </c>
       <c r="H58" s="9">
-        <v>0</v>
-      </c>
-      <c r="I58" s="8">
-        <v>-100</v>
+        <v>7.3599999999999999E-2</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J58" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K58" s="9">
-        <v>3.8E-3</v>
-      </c>
-      <c r="L58" s="8">
-        <v>-99.6</v>
+        <v>7.3599999999999999E-2</v>
+      </c>
+      <c r="L58" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M58" s="9">
-        <v>0</v>
-      </c>
-      <c r="N58" s="8">
-        <v>-100</v>
+        <v>7.3599999999999999E-2</v>
+      </c>
+      <c r="N58" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O58" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P58" s="9">
-        <v>3.8E-3</v>
-      </c>
-      <c r="Q58" s="8">
-        <v>-99.6</v>
+        <v>7.3599999999999999E-2</v>
+      </c>
+      <c r="Q58" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
-        <v>43040</v>
+        <v>43070</v>
       </c>
       <c r="B59" s="7">
-        <v>174</v>
+        <v>152.5</v>
       </c>
       <c r="C59" s="7">
-        <v>151.5</v>
+        <v>150.5</v>
       </c>
       <c r="D59" s="7">
-        <v>176.5</v>
+        <v>156</v>
       </c>
       <c r="E59" s="7">
-        <v>148.5</v>
+        <v>135</v>
       </c>
       <c r="F59" s="8">
-        <v>-20.5</v>
+        <v>-1</v>
       </c>
       <c r="G59" s="8">
-        <v>-11.92</v>
+        <v>-0.66</v>
       </c>
       <c r="H59" s="9">
-        <v>1E-4</v>
-      </c>
-      <c r="I59" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J59" s="8">
-        <v>-72.2</v>
+        <v>0</v>
+      </c>
+      <c r="I59" s="8">
+        <v>-100</v>
+      </c>
+      <c r="J59" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K59" s="9">
         <v>3.8E-3</v>
@@ -4282,13 +4282,13 @@
         <v>-99.6</v>
       </c>
       <c r="M59" s="9">
-        <v>1E-4</v>
-      </c>
-      <c r="N59" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O59" s="8">
-        <v>-72.2</v>
+        <v>0</v>
+      </c>
+      <c r="N59" s="8">
+        <v>-100</v>
+      </c>
+      <c r="O59" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P59" s="9">
         <v>3.8E-3</v>
@@ -4299,52 +4299,52 @@
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
-        <v>43009</v>
+        <v>43040</v>
       </c>
       <c r="B60" s="7">
         <v>174</v>
       </c>
       <c r="C60" s="7">
-        <v>172</v>
+        <v>151.5</v>
       </c>
       <c r="D60" s="7">
-        <v>177</v>
+        <v>176.5</v>
       </c>
       <c r="E60" s="7">
-        <v>145.5</v>
+        <v>148.5</v>
       </c>
       <c r="F60" s="8">
-        <v>-1</v>
+        <v>-20.5</v>
       </c>
       <c r="G60" s="8">
-        <v>-0.57999999999999996</v>
+        <v>-11.92</v>
       </c>
       <c r="H60" s="9">
-        <v>0</v>
+        <v>1E-4</v>
       </c>
       <c r="I60" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J60" s="9" t="s">
-        <v>17</v>
+      <c r="J60" s="8">
+        <v>-72.2</v>
       </c>
       <c r="K60" s="9">
-        <v>3.7000000000000002E-3</v>
+        <v>3.8E-3</v>
       </c>
       <c r="L60" s="8">
         <v>-99.6</v>
       </c>
       <c r="M60" s="9">
-        <v>0</v>
+        <v>1E-4</v>
       </c>
       <c r="N60" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O60" s="9" t="s">
-        <v>17</v>
+      <c r="O60" s="8">
+        <v>-72.2</v>
       </c>
       <c r="P60" s="9">
-        <v>3.7000000000000002E-3</v>
+        <v>3.8E-3</v>
       </c>
       <c r="Q60" s="8">
         <v>-99.6</v>
@@ -4352,25 +4352,25 @@
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
-        <v>42979</v>
+        <v>43009</v>
       </c>
       <c r="B61" s="7">
-        <v>192.5</v>
+        <v>174</v>
       </c>
       <c r="C61" s="7">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D61" s="7">
-        <v>213</v>
+        <v>177</v>
       </c>
       <c r="E61" s="7">
-        <v>171</v>
+        <v>145.5</v>
       </c>
       <c r="F61" s="8">
-        <v>-17</v>
+        <v>-1</v>
       </c>
       <c r="G61" s="8">
-        <v>-8.9499999999999993</v>
+        <v>-0.57999999999999996</v>
       </c>
       <c r="H61" s="9">
         <v>0</v>
@@ -4405,25 +4405,25 @@
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
-        <v>42948</v>
+        <v>42979</v>
       </c>
       <c r="B62" s="7">
-        <v>217</v>
+        <v>192.5</v>
       </c>
       <c r="C62" s="7">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="D62" s="7">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E62" s="7">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F62" s="8">
-        <v>-25</v>
+        <v>-17</v>
       </c>
       <c r="G62" s="8">
-        <v>-11.63</v>
+        <v>-8.9499999999999993</v>
       </c>
       <c r="H62" s="9">
         <v>0</v>
@@ -4458,25 +4458,25 @@
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>42917</v>
+        <v>42948</v>
       </c>
       <c r="B63" s="7">
-        <v>240.5</v>
+        <v>217</v>
       </c>
       <c r="C63" s="7">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="D63" s="7">
-        <v>243.5</v>
+        <v>217</v>
       </c>
       <c r="E63" s="7">
-        <v>202.5</v>
+        <v>173</v>
       </c>
       <c r="F63" s="8">
-        <v>-26</v>
+        <v>-25</v>
       </c>
       <c r="G63" s="8">
-        <v>-10.79</v>
+        <v>-11.63</v>
       </c>
       <c r="H63" s="9">
         <v>0</v>
@@ -4511,31 +4511,31 @@
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>42887</v>
+        <v>42917</v>
       </c>
       <c r="B64" s="7">
-        <v>254</v>
+        <v>240.5</v>
       </c>
       <c r="C64" s="7">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="D64" s="7">
-        <v>269.5</v>
+        <v>243.5</v>
       </c>
       <c r="E64" s="7">
-        <v>238</v>
+        <v>202.5</v>
       </c>
       <c r="F64" s="8">
-        <v>-15.5</v>
+        <v>-26</v>
       </c>
       <c r="G64" s="8">
-        <v>-6.04</v>
+        <v>-10.79</v>
       </c>
       <c r="H64" s="9">
         <v>0</v>
       </c>
-      <c r="I64" s="8">
-        <v>-100</v>
+      <c r="I64" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J64" s="9" t="s">
         <v>17</v>
@@ -4549,8 +4549,8 @@
       <c r="M64" s="9">
         <v>0</v>
       </c>
-      <c r="N64" s="8">
-        <v>-100</v>
+      <c r="N64" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O64" s="9" t="s">
         <v>17</v>
@@ -4564,34 +4564,34 @@
     </row>
     <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
-        <v>42856</v>
+        <v>42887</v>
       </c>
       <c r="B65" s="7">
-        <v>286</v>
+        <v>254</v>
       </c>
       <c r="C65" s="7">
-        <v>256.5</v>
+        <v>241</v>
       </c>
       <c r="D65" s="7">
-        <v>286</v>
+        <v>269.5</v>
       </c>
       <c r="E65" s="7">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="F65" s="8">
-        <v>-27.5</v>
+        <v>-15.5</v>
       </c>
       <c r="G65" s="8">
-        <v>-9.68</v>
+        <v>-6.04</v>
       </c>
       <c r="H65" s="9">
-        <v>3.7000000000000002E-3</v>
-      </c>
-      <c r="I65" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J65" s="8">
-        <v>-99.6</v>
+        <v>0</v>
+      </c>
+      <c r="I65" s="8">
+        <v>-100</v>
+      </c>
+      <c r="J65" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K65" s="9">
         <v>3.7000000000000002E-3</v>
@@ -4600,13 +4600,13 @@
         <v>-99.6</v>
       </c>
       <c r="M65" s="9">
-        <v>3.7000000000000002E-3</v>
-      </c>
-      <c r="N65" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O65" s="8">
-        <v>-99.6</v>
+        <v>0</v>
+      </c>
+      <c r="N65" s="8">
+        <v>-100</v>
+      </c>
+      <c r="O65" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P65" s="9">
         <v>3.7000000000000002E-3</v>
@@ -4617,78 +4617,78 @@
     </row>
     <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
-        <v>42826</v>
+        <v>42856</v>
       </c>
       <c r="B66" s="7">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="C66" s="7">
-        <v>284</v>
+        <v>256.5</v>
       </c>
       <c r="D66" s="7">
-        <v>288.5</v>
+        <v>286</v>
       </c>
       <c r="E66" s="7">
-        <v>258</v>
-      </c>
-      <c r="F66" s="10">
-        <v>11</v>
-      </c>
-      <c r="G66" s="10">
-        <v>4.03</v>
+        <v>253</v>
+      </c>
+      <c r="F66" s="8">
+        <v>-27.5</v>
+      </c>
+      <c r="G66" s="8">
+        <v>-9.68</v>
       </c>
       <c r="H66" s="9">
-        <v>0</v>
+        <v>3.7000000000000002E-3</v>
       </c>
       <c r="I66" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J66" s="9" t="s">
-        <v>17</v>
+      <c r="J66" s="8">
+        <v>-99.6</v>
       </c>
       <c r="K66" s="9">
-        <v>0</v>
-      </c>
-      <c r="L66" s="9" t="s">
-        <v>17</v>
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="L66" s="8">
+        <v>-99.6</v>
       </c>
       <c r="M66" s="9">
-        <v>0</v>
+        <v>3.7000000000000002E-3</v>
       </c>
       <c r="N66" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O66" s="9" t="s">
-        <v>17</v>
+      <c r="O66" s="8">
+        <v>-99.6</v>
       </c>
       <c r="P66" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="9" t="s">
-        <v>17</v>
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="Q66" s="8">
+        <v>-99.6</v>
       </c>
     </row>
     <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
-        <v>42795</v>
+        <v>42826</v>
       </c>
       <c r="B67" s="7">
-        <v>350</v>
+        <v>271</v>
       </c>
       <c r="C67" s="7">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="D67" s="7">
-        <v>368</v>
+        <v>288.5</v>
       </c>
       <c r="E67" s="7">
-        <v>272</v>
-      </c>
-      <c r="F67" s="8">
-        <v>-76.5</v>
-      </c>
-      <c r="G67" s="8">
-        <v>-21.89</v>
+        <v>258</v>
+      </c>
+      <c r="F67" s="10">
+        <v>11</v>
+      </c>
+      <c r="G67" s="10">
+        <v>4.03</v>
       </c>
       <c r="H67" s="9">
         <v>0</v>
@@ -4723,25 +4723,25 @@
     </row>
     <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
-        <v>42767</v>
+        <v>42795</v>
       </c>
       <c r="B68" s="7">
-        <v>295</v>
+        <v>350</v>
       </c>
       <c r="C68" s="7">
-        <v>349.5</v>
+        <v>273</v>
       </c>
       <c r="D68" s="7">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="E68" s="7">
-        <v>277.5</v>
-      </c>
-      <c r="F68" s="10">
-        <v>59.5</v>
-      </c>
-      <c r="G68" s="10">
-        <v>20.52</v>
+        <v>272</v>
+      </c>
+      <c r="F68" s="8">
+        <v>-76.5</v>
+      </c>
+      <c r="G68" s="8">
+        <v>-21.89</v>
       </c>
       <c r="H68" s="9">
         <v>0</v>
@@ -4776,25 +4776,25 @@
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
-        <v>42736</v>
+        <v>42767</v>
       </c>
       <c r="B69" s="7">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C69" s="7">
-        <v>290</v>
+        <v>349.5</v>
       </c>
       <c r="D69" s="7">
-        <v>311</v>
+        <v>359</v>
       </c>
       <c r="E69" s="7">
-        <v>248</v>
+        <v>277.5</v>
       </c>
       <c r="F69" s="10">
-        <v>5</v>
+        <v>59.5</v>
       </c>
       <c r="G69" s="10">
-        <v>1.75</v>
+        <v>20.52</v>
       </c>
       <c r="H69" s="9">
         <v>0</v>
@@ -4829,37 +4829,37 @@
     </row>
     <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
-        <v>42705</v>
+        <v>42736</v>
       </c>
       <c r="B70" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C70" s="7">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="D70" s="7">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="E70" s="7">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="F70" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G70" s="10">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="H70" s="9">
         <v>0</v>
       </c>
-      <c r="I70" s="8">
-        <v>-100</v>
+      <c r="I70" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J70" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K70" s="9">
-        <v>0.92400000000000004</v>
+        <v>0</v>
       </c>
       <c r="L70" s="9" t="s">
         <v>17</v>
@@ -4867,14 +4867,14 @@
       <c r="M70" s="9">
         <v>0</v>
       </c>
-      <c r="N70" s="8">
-        <v>-100</v>
+      <c r="N70" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O70" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P70" s="9">
-        <v>0.92400000000000004</v>
+        <v>0</v>
       </c>
       <c r="Q70" s="9" t="s">
         <v>17</v>
@@ -4882,31 +4882,31 @@
     </row>
     <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
-        <v>42675</v>
+        <v>42705</v>
       </c>
       <c r="B71" s="7">
-        <v>326.5</v>
+        <v>284</v>
       </c>
       <c r="C71" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D71" s="7">
-        <v>327.5</v>
+        <v>298</v>
       </c>
       <c r="E71" s="7">
-        <v>268</v>
-      </c>
-      <c r="F71" s="8">
-        <v>-49.5</v>
-      </c>
-      <c r="G71" s="8">
-        <v>-14.98</v>
+        <v>226</v>
+      </c>
+      <c r="F71" s="10">
+        <v>4</v>
+      </c>
+      <c r="G71" s="10">
+        <v>1.42</v>
       </c>
       <c r="H71" s="9">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="I71" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I71" s="8">
+        <v>-100</v>
       </c>
       <c r="J71" s="9" t="s">
         <v>17</v>
@@ -4918,10 +4918,10 @@
         <v>17</v>
       </c>
       <c r="M71" s="9">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="N71" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N71" s="8">
+        <v>-100</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>17</v>
@@ -4935,28 +4935,28 @@
     </row>
     <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
-        <v>42644</v>
+        <v>42675</v>
       </c>
       <c r="B72" s="7">
-        <v>396</v>
+        <v>326.5</v>
       </c>
       <c r="C72" s="7">
-        <v>330.5</v>
+        <v>281</v>
       </c>
       <c r="D72" s="7">
-        <v>399</v>
+        <v>327.5</v>
       </c>
       <c r="E72" s="7">
-        <v>321</v>
+        <v>268</v>
       </c>
       <c r="F72" s="8">
-        <v>-60</v>
+        <v>-49.5</v>
       </c>
       <c r="G72" s="8">
-        <v>-15.36</v>
+        <v>-14.98</v>
       </c>
       <c r="H72" s="9">
-        <v>0</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="I72" s="9" t="s">
         <v>17</v>
@@ -4971,7 +4971,7 @@
         <v>17</v>
       </c>
       <c r="M72" s="9">
-        <v>0</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="N72" s="9" t="s">
         <v>17</v>
@@ -4988,25 +4988,25 @@
     </row>
     <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
-        <v>42614</v>
+        <v>42644</v>
       </c>
       <c r="B73" s="7">
         <v>396</v>
       </c>
       <c r="C73" s="7">
-        <v>390.5</v>
+        <v>330.5</v>
       </c>
       <c r="D73" s="7">
-        <v>424</v>
+        <v>399</v>
       </c>
       <c r="E73" s="7">
-        <v>367</v>
+        <v>321</v>
       </c>
       <c r="F73" s="8">
-        <v>-6.5</v>
+        <v>-60</v>
       </c>
       <c r="G73" s="8">
-        <v>-1.64</v>
+        <v>-15.36</v>
       </c>
       <c r="H73" s="9">
         <v>0</v>
@@ -5041,25 +5041,25 @@
     </row>
     <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
-        <v>42583</v>
+        <v>42614</v>
       </c>
       <c r="B74" s="7">
-        <v>493.5</v>
+        <v>396</v>
       </c>
       <c r="C74" s="7">
-        <v>397</v>
+        <v>390.5</v>
       </c>
       <c r="D74" s="7">
-        <v>506</v>
+        <v>424</v>
       </c>
       <c r="E74" s="7">
-        <v>385.5</v>
+        <v>367</v>
       </c>
       <c r="F74" s="8">
-        <v>-96</v>
+        <v>-6.5</v>
       </c>
       <c r="G74" s="8">
-        <v>-19.47</v>
+        <v>-1.64</v>
       </c>
       <c r="H74" s="9">
         <v>0</v>
@@ -5094,25 +5094,25 @@
     </row>
     <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
-        <v>42552</v>
+        <v>42583</v>
       </c>
       <c r="B75" s="7">
-        <v>514</v>
+        <v>493.5</v>
       </c>
       <c r="C75" s="7">
-        <v>493</v>
+        <v>397</v>
       </c>
       <c r="D75" s="7">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="E75" s="7">
-        <v>464</v>
+        <v>385.5</v>
       </c>
       <c r="F75" s="8">
-        <v>-17</v>
+        <v>-96</v>
       </c>
       <c r="G75" s="8">
-        <v>-3.33</v>
+        <v>-19.47</v>
       </c>
       <c r="H75" s="9">
         <v>0</v>
@@ -5147,31 +5147,31 @@
     </row>
     <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
-        <v>42522</v>
+        <v>42552</v>
       </c>
       <c r="B76" s="7">
-        <v>608</v>
+        <v>514</v>
       </c>
       <c r="C76" s="7">
-        <v>510</v>
+        <v>493</v>
       </c>
       <c r="D76" s="7">
-        <v>630</v>
+        <v>517</v>
       </c>
       <c r="E76" s="7">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="F76" s="8">
-        <v>-98</v>
+        <v>-17</v>
       </c>
       <c r="G76" s="8">
-        <v>-16.12</v>
+        <v>-3.33</v>
       </c>
       <c r="H76" s="9">
         <v>0</v>
       </c>
-      <c r="I76" s="8">
-        <v>-100</v>
+      <c r="I76" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J76" s="9" t="s">
         <v>17</v>
@@ -5185,8 +5185,8 @@
       <c r="M76" s="9">
         <v>0</v>
       </c>
-      <c r="N76" s="8">
-        <v>-100</v>
+      <c r="N76" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O76" s="9" t="s">
         <v>17</v>
@@ -5200,31 +5200,31 @@
     </row>
     <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
-        <v>42491</v>
+        <v>42522</v>
       </c>
       <c r="B77" s="7">
-        <v>380</v>
+        <v>608</v>
       </c>
       <c r="C77" s="7">
-        <v>608</v>
+        <v>510</v>
       </c>
       <c r="D77" s="7">
-        <v>608</v>
+        <v>630</v>
       </c>
       <c r="E77" s="7">
-        <v>351</v>
-      </c>
-      <c r="F77" s="10">
-        <v>227.5</v>
-      </c>
-      <c r="G77" s="10">
-        <v>59.79</v>
+        <v>461</v>
+      </c>
+      <c r="F77" s="8">
+        <v>-98</v>
+      </c>
+      <c r="G77" s="8">
+        <v>-16.12</v>
       </c>
       <c r="H77" s="9">
-        <v>0.92400000000000004</v>
-      </c>
-      <c r="I77" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I77" s="8">
+        <v>-100</v>
       </c>
       <c r="J77" s="9" t="s">
         <v>17</v>
@@ -5236,10 +5236,10 @@
         <v>17</v>
       </c>
       <c r="M77" s="9">
-        <v>0.92400000000000004</v>
-      </c>
-      <c r="N77" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N77" s="8">
+        <v>-100</v>
       </c>
       <c r="O77" s="9" t="s">
         <v>17</v>
@@ -5253,28 +5253,28 @@
     </row>
     <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
-        <v>42461</v>
+        <v>42491</v>
       </c>
       <c r="B78" s="7">
-        <v>434.5</v>
+        <v>380</v>
       </c>
       <c r="C78" s="7">
-        <v>380.5</v>
+        <v>608</v>
       </c>
       <c r="D78" s="7">
-        <v>434.5</v>
+        <v>608</v>
       </c>
       <c r="E78" s="7">
-        <v>321</v>
-      </c>
-      <c r="F78" s="8">
-        <v>-14.5</v>
-      </c>
-      <c r="G78" s="8">
-        <v>-3.67</v>
+        <v>351</v>
+      </c>
+      <c r="F78" s="10">
+        <v>227.5</v>
+      </c>
+      <c r="G78" s="10">
+        <v>59.79</v>
       </c>
       <c r="H78" s="9">
-        <v>0</v>
+        <v>0.92400000000000004</v>
       </c>
       <c r="I78" s="9" t="s">
         <v>17</v>
@@ -5283,13 +5283,13 @@
         <v>17</v>
       </c>
       <c r="K78" s="9">
-        <v>0</v>
+        <v>0.92400000000000004</v>
       </c>
       <c r="L78" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M78" s="9">
-        <v>0</v>
+        <v>0.92400000000000004</v>
       </c>
       <c r="N78" s="9" t="s">
         <v>17</v>
@@ -5298,7 +5298,7 @@
         <v>17</v>
       </c>
       <c r="P78" s="9">
-        <v>0</v>
+        <v>0.92400000000000004</v>
       </c>
       <c r="Q78" s="9" t="s">
         <v>17</v>
@@ -5306,25 +5306,25 @@
     </row>
     <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
-        <v>42430</v>
+        <v>42461</v>
       </c>
       <c r="B79" s="7">
-        <v>450</v>
+        <v>434.5</v>
       </c>
       <c r="C79" s="7">
-        <v>395</v>
+        <v>380.5</v>
       </c>
       <c r="D79" s="7">
-        <v>465</v>
+        <v>434.5</v>
       </c>
       <c r="E79" s="7">
-        <v>351</v>
+        <v>321</v>
       </c>
       <c r="F79" s="8">
-        <v>-68</v>
+        <v>-14.5</v>
       </c>
       <c r="G79" s="8">
-        <v>-14.69</v>
+        <v>-3.67</v>
       </c>
       <c r="H79" s="9">
         <v>0</v>
@@ -5359,25 +5359,25 @@
     </row>
     <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
-        <v>42401</v>
+        <v>42430</v>
       </c>
       <c r="B80" s="7">
-        <v>641</v>
+        <v>450</v>
       </c>
       <c r="C80" s="7">
-        <v>463</v>
+        <v>395</v>
       </c>
       <c r="D80" s="7">
-        <v>718</v>
+        <v>465</v>
       </c>
       <c r="E80" s="7">
-        <v>405.5</v>
+        <v>351</v>
       </c>
       <c r="F80" s="8">
-        <v>-172</v>
+        <v>-68</v>
       </c>
       <c r="G80" s="8">
-        <v>-27.09</v>
+        <v>-14.69</v>
       </c>
       <c r="H80" s="9">
         <v>0</v>
@@ -5412,25 +5412,25 @@
     </row>
     <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
-        <v>42370</v>
+        <v>42401</v>
       </c>
       <c r="B81" s="7">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C81" s="7">
-        <v>635</v>
+        <v>463</v>
       </c>
       <c r="D81" s="7">
-        <v>653</v>
+        <v>718</v>
       </c>
       <c r="E81" s="7">
-        <v>528</v>
+        <v>405.5</v>
       </c>
       <c r="F81" s="8">
-        <v>-20</v>
+        <v>-172</v>
       </c>
       <c r="G81" s="8">
-        <v>-3.05</v>
+        <v>-27.09</v>
       </c>
       <c r="H81" s="9">
         <v>0</v>
@@ -5465,25 +5465,25 @@
     </row>
     <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
-        <v>42339</v>
+        <v>42370</v>
       </c>
       <c r="B82" s="7">
-        <v>670</v>
+        <v>640</v>
       </c>
       <c r="C82" s="7">
-        <v>655</v>
+        <v>635</v>
       </c>
       <c r="D82" s="7">
-        <v>755</v>
+        <v>653</v>
       </c>
       <c r="E82" s="7">
-        <v>630</v>
+        <v>528</v>
       </c>
       <c r="F82" s="8">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="G82" s="8">
-        <v>-3.11</v>
+        <v>-3.05</v>
       </c>
       <c r="H82" s="9">
         <v>0</v>
@@ -5518,25 +5518,25 @@
     </row>
     <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
-        <v>42309</v>
+        <v>42339</v>
       </c>
       <c r="B83" s="7">
-        <v>402</v>
+        <v>670</v>
       </c>
       <c r="C83" s="7">
-        <v>676</v>
+        <v>655</v>
       </c>
       <c r="D83" s="7">
-        <v>676</v>
+        <v>755</v>
       </c>
       <c r="E83" s="7">
-        <v>401</v>
-      </c>
-      <c r="F83" s="10">
-        <v>274</v>
-      </c>
-      <c r="G83" s="10">
-        <v>68.16</v>
+        <v>630</v>
+      </c>
+      <c r="F83" s="8">
+        <v>-21</v>
+      </c>
+      <c r="G83" s="8">
+        <v>-3.11</v>
       </c>
       <c r="H83" s="9">
         <v>0</v>
@@ -5571,25 +5571,25 @@
     </row>
     <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
-        <v>42278</v>
+        <v>42309</v>
       </c>
       <c r="B84" s="7">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C84" s="7">
-        <v>402</v>
+        <v>676</v>
       </c>
       <c r="D84" s="7">
-        <v>422</v>
+        <v>676</v>
       </c>
       <c r="E84" s="7">
-        <v>358</v>
+        <v>401</v>
       </c>
       <c r="F84" s="10">
-        <v>20</v>
+        <v>274</v>
       </c>
       <c r="G84" s="10">
-        <v>5.24</v>
+        <v>68.16</v>
       </c>
       <c r="H84" s="9">
         <v>0</v>
@@ -5624,25 +5624,25 @@
     </row>
     <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
-        <v>42248</v>
+        <v>42278</v>
       </c>
       <c r="B85" s="7">
-        <v>274</v>
+        <v>382</v>
       </c>
       <c r="C85" s="7">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="D85" s="7">
-        <v>387</v>
+        <v>422</v>
       </c>
       <c r="E85" s="7">
-        <v>263</v>
+        <v>358</v>
       </c>
       <c r="F85" s="10">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="G85" s="10">
-        <v>39.42</v>
+        <v>5.24</v>
       </c>
       <c r="H85" s="9">
         <v>0</v>
@@ -5677,25 +5677,25 @@
     </row>
     <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
-        <v>42217</v>
+        <v>42248</v>
       </c>
       <c r="B86" s="7">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="C86" s="7">
-        <v>274</v>
+        <v>382</v>
       </c>
       <c r="D86" s="7">
-        <v>310.5</v>
+        <v>387</v>
       </c>
       <c r="E86" s="7">
-        <v>250</v>
-      </c>
-      <c r="F86" s="8">
-        <v>-19.5</v>
-      </c>
-      <c r="G86" s="8">
-        <v>-6.64</v>
+        <v>263</v>
+      </c>
+      <c r="F86" s="10">
+        <v>108</v>
+      </c>
+      <c r="G86" s="10">
+        <v>39.42</v>
       </c>
       <c r="H86" s="9">
         <v>0</v>
@@ -5730,25 +5730,25 @@
     </row>
     <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
-        <v>42186</v>
+        <v>42217</v>
       </c>
       <c r="B87" s="7">
-        <v>293.5</v>
+        <v>292</v>
       </c>
       <c r="C87" s="7">
-        <v>293.5</v>
+        <v>274</v>
       </c>
       <c r="D87" s="7">
-        <v>321.5</v>
+        <v>310.5</v>
       </c>
       <c r="E87" s="7">
-        <v>273.5</v>
-      </c>
-      <c r="F87" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="G87" s="10">
-        <v>0.51</v>
+        <v>250</v>
+      </c>
+      <c r="F87" s="8">
+        <v>-19.5</v>
+      </c>
+      <c r="G87" s="8">
+        <v>-6.64</v>
       </c>
       <c r="H87" s="9">
         <v>0</v>
@@ -5783,25 +5783,25 @@
     </row>
     <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
-        <v>42156</v>
+        <v>42186</v>
       </c>
       <c r="B88" s="7">
-        <v>340</v>
+        <v>293.5</v>
       </c>
       <c r="C88" s="7">
-        <v>292</v>
+        <v>293.5</v>
       </c>
       <c r="D88" s="7">
-        <v>343.5</v>
+        <v>321.5</v>
       </c>
       <c r="E88" s="7">
-        <v>282</v>
-      </c>
-      <c r="F88" s="8">
-        <v>-45</v>
-      </c>
-      <c r="G88" s="8">
-        <v>-13.35</v>
+        <v>273.5</v>
+      </c>
+      <c r="F88" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="G88" s="10">
+        <v>0.51</v>
       </c>
       <c r="H88" s="9">
         <v>0</v>
@@ -5836,25 +5836,25 @@
     </row>
     <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
-        <v>42125</v>
+        <v>42156</v>
       </c>
       <c r="B89" s="7">
-        <v>338.5</v>
+        <v>340</v>
       </c>
       <c r="C89" s="7">
-        <v>337</v>
+        <v>292</v>
       </c>
       <c r="D89" s="7">
-        <v>343</v>
+        <v>343.5</v>
       </c>
       <c r="E89" s="7">
-        <v>296</v>
-      </c>
-      <c r="F89" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="G89" s="10">
-        <v>0.15</v>
+        <v>282</v>
+      </c>
+      <c r="F89" s="8">
+        <v>-45</v>
+      </c>
+      <c r="G89" s="8">
+        <v>-13.35</v>
       </c>
       <c r="H89" s="9">
         <v>0</v>
@@ -5889,25 +5889,25 @@
     </row>
     <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
-        <v>42095</v>
+        <v>42125</v>
       </c>
       <c r="B90" s="7">
-        <v>320</v>
+        <v>338.5</v>
       </c>
       <c r="C90" s="7">
-        <v>336.5</v>
+        <v>337</v>
       </c>
       <c r="D90" s="7">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="E90" s="7">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="F90" s="10">
-        <v>12</v>
+        <v>0.5</v>
       </c>
       <c r="G90" s="10">
-        <v>3.7</v>
+        <v>0.15</v>
       </c>
       <c r="H90" s="9">
         <v>0</v>
@@ -5942,25 +5942,25 @@
     </row>
     <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
-        <v>42064</v>
+        <v>42095</v>
       </c>
       <c r="B91" s="7">
-        <v>367</v>
+        <v>320</v>
       </c>
       <c r="C91" s="7">
-        <v>324.5</v>
+        <v>336.5</v>
       </c>
       <c r="D91" s="7">
-        <v>378</v>
+        <v>351</v>
       </c>
       <c r="E91" s="7">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="F91" s="10">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="G91" s="10">
-        <v>4.68</v>
+        <v>3.7</v>
       </c>
       <c r="H91" s="9">
         <v>0</v>
@@ -5995,25 +5995,25 @@
     </row>
     <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
-        <v>42036</v>
-      </c>
-      <c r="B92" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D92" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E92" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F92" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G92" s="9" t="s">
-        <v>17</v>
+        <v>42064</v>
+      </c>
+      <c r="B92" s="7">
+        <v>367</v>
+      </c>
+      <c r="C92" s="7">
+        <v>324.5</v>
+      </c>
+      <c r="D92" s="7">
+        <v>378</v>
+      </c>
+      <c r="E92" s="7">
+        <v>312</v>
+      </c>
+      <c r="F92" s="10">
+        <v>14.5</v>
+      </c>
+      <c r="G92" s="10">
+        <v>4.68</v>
       </c>
       <c r="H92" s="9">
         <v>0</v>
@@ -6048,7 +6048,7 @@
     </row>
     <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
-        <v>42005</v>
+        <v>42036</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>17</v>
@@ -6101,7 +6101,7 @@
     </row>
     <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
-        <v>41974</v>
+        <v>42005</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>17</v>
@@ -6154,7 +6154,7 @@
     </row>
     <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
-        <v>41944</v>
+        <v>41974</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>17</v>
@@ -6207,7 +6207,7 @@
     </row>
     <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
-        <v>41913</v>
+        <v>41944</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>17</v>
@@ -6260,7 +6260,7 @@
     </row>
     <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
-        <v>41883</v>
+        <v>41913</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>17</v>
@@ -6313,7 +6313,7 @@
     </row>
     <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
-        <v>41852</v>
+        <v>41883</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>17</v>
@@ -6366,7 +6366,7 @@
     </row>
     <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
-        <v>41821</v>
+        <v>41852</v>
       </c>
       <c r="B99" s="7" t="s">
         <v>17</v>
@@ -6419,7 +6419,7 @@
     </row>
     <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
-        <v>41791</v>
+        <v>41821</v>
       </c>
       <c r="B100" s="7" t="s">
         <v>17</v>
@@ -6472,7 +6472,7 @@
     </row>
     <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
-        <v>41760</v>
+        <v>41791</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>17</v>
@@ -6525,7 +6525,7 @@
     </row>
     <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
-        <v>41730</v>
+        <v>41760</v>
       </c>
       <c r="B102" s="7" t="s">
         <v>17</v>
@@ -6578,7 +6578,7 @@
     </row>
     <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
-        <v>41699</v>
+        <v>41730</v>
       </c>
       <c r="B103" s="7" t="s">
         <v>17</v>
@@ -6631,7 +6631,7 @@
     </row>
     <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
-        <v>41671</v>
+        <v>41699</v>
       </c>
       <c r="B104" s="7" t="s">
         <v>17</v>
@@ -6684,7 +6684,7 @@
     </row>
     <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
-        <v>41640</v>
+        <v>41671</v>
       </c>
       <c r="B105" s="7" t="s">
         <v>17</v>
@@ -6737,7 +6737,7 @@
     </row>
     <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
-        <v>41609</v>
+        <v>41640</v>
       </c>
       <c r="B106" s="7" t="s">
         <v>17</v>
@@ -6790,7 +6790,7 @@
     </row>
     <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
-        <v>41579</v>
+        <v>41609</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>17</v>
@@ -6843,7 +6843,7 @@
     </row>
     <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
-        <v>41548</v>
+        <v>41579</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>17</v>
@@ -6896,7 +6896,7 @@
     </row>
     <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
-        <v>41518</v>
+        <v>41548</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>17</v>
@@ -6949,7 +6949,7 @@
     </row>
     <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
-        <v>41487</v>
+        <v>41518</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>17</v>
@@ -7002,7 +7002,7 @@
     </row>
     <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
-        <v>41456</v>
+        <v>41487</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>17</v>
@@ -7055,7 +7055,7 @@
     </row>
     <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
-        <v>41426</v>
+        <v>41456</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>17</v>
@@ -7108,7 +7108,7 @@
     </row>
     <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
-        <v>41395</v>
+        <v>41426</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>17</v>
@@ -7161,7 +7161,7 @@
     </row>
     <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
-        <v>41365</v>
+        <v>41395</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>17</v>
@@ -7214,7 +7214,7 @@
     </row>
     <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
-        <v>41334</v>
+        <v>41365</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>17</v>
@@ -7267,7 +7267,7 @@
     </row>
     <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
-        <v>41306</v>
+        <v>41334</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>17</v>
@@ -7320,7 +7320,7 @@
     </row>
     <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
-        <v>41275</v>
+        <v>41306</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>17</v>
@@ -7373,7 +7373,7 @@
     </row>
     <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
-        <v>41244</v>
+        <v>41275</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>17</v>
@@ -7408,8 +7408,8 @@
       <c r="L118" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="M118" s="9" t="s">
-        <v>17</v>
+      <c r="M118" s="9">
+        <v>0</v>
       </c>
       <c r="N118" s="9" t="s">
         <v>17</v>
@@ -7417,8 +7417,8 @@
       <c r="O118" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="P118" s="9" t="s">
-        <v>17</v>
+      <c r="P118" s="9">
+        <v>0</v>
       </c>
       <c r="Q118" s="9" t="s">
         <v>17</v>
@@ -7426,7 +7426,7 @@
     </row>
     <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
-        <v>41214</v>
+        <v>41244</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>17</v>
@@ -7479,7 +7479,7 @@
     </row>
     <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
-        <v>41183</v>
+        <v>41214</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>17</v>
@@ -7532,7 +7532,7 @@
     </row>
     <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
-        <v>41153</v>
+        <v>41183</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>17</v>
@@ -7585,7 +7585,7 @@
     </row>
     <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
-        <v>41122</v>
+        <v>41153</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>17</v>
@@ -7638,7 +7638,7 @@
     </row>
     <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
-        <v>41091</v>
+        <v>41122</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>17</v>
@@ -7691,7 +7691,7 @@
     </row>
     <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
-        <v>41061</v>
+        <v>41091</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>17</v>
@@ -7744,54 +7744,107 @@
     </row>
     <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
+        <v>41061</v>
+      </c>
+      <c r="B125" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F125" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G125" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H125" s="9">
+        <v>0</v>
+      </c>
+      <c r="I125" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J125" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K125" s="9">
+        <v>0</v>
+      </c>
+      <c r="L125" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M125" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N125" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O125" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P125" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q125" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A126" s="6">
         <v>41030</v>
       </c>
-      <c r="B125" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C125" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D125" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E125" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F125" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G125" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H125" s="9">
-        <v>0</v>
-      </c>
-      <c r="I125" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J125" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K125" s="9">
-        <v>0</v>
-      </c>
-      <c r="L125" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M125" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="N125" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O125" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P125" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q125" s="9" t="s">
+      <c r="B126" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E126" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H126" s="9">
+        <v>0</v>
+      </c>
+      <c r="I126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K126" s="9">
+        <v>0</v>
+      </c>
+      <c r="L126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q126" s="9" t="s">
         <v>17</v>
       </c>
     </row>
